--- a/CATLEC.xlsx
+++ b/CATLEC.xlsx
@@ -8,25 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edison\Desktop\CATLEC\Codigo CATLEC - backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E3A4FF-93C3-47DA-89CF-FEBEC7DAD5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E325EB8-2AD6-4960-82A5-A3F4BB9C5795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="TD BD" sheetId="3" r:id="rId1"/>
     <sheet name="BD" sheetId="1" r:id="rId2"/>
-    <sheet name="OF" sheetId="4" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="7" r:id="rId4"/>
-    <sheet name="Hoja4" sheetId="5" r:id="rId5"/>
-    <sheet name="Consideraciones" sheetId="6" r:id="rId6"/>
+    <sheet name="Hoja2" sheetId="8" r:id="rId3"/>
+    <sheet name="OF" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="7" r:id="rId5"/>
+    <sheet name="Hoja4" sheetId="5" r:id="rId6"/>
+    <sheet name="Consideraciones" sheetId="6" r:id="rId7"/>
+    <sheet name="EFE" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BD!$AK$1:$AK$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -73,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4913" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="1956">
   <si>
     <t>Código proyecto</t>
   </si>
@@ -6077,16 +6079,158 @@
   <si>
     <t>https://www.google.com/maps/embed?pb=!4v1785290150295!6m8!1m7!1sicThNaSV4Im5zlPp8Z8EwA!2m2!1d-36.8134299744532!2d-73.13195268530824!3f185.4989004980487!4f5.353377164855985!5f0.7820865974627469</t>
   </si>
+  <si>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>Institucion mandante</t>
+  </si>
+  <si>
+    <t>Fuente  de inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversion (USD) </t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>1;2;3;4;5;6;7;8;9;10</t>
+  </si>
+  <si>
+    <t>Extension Tren Limache - Puerto a Quillota y La Calera</t>
+  </si>
+  <si>
+    <t>EFE</t>
+  </si>
+  <si>
+    <t>https://www.efe.cl/proyectos/</t>
+  </si>
+  <si>
+    <t>Nuevo Servicio Tren Chillan - Estacion Central</t>
+  </si>
+  <si>
+    <t>Mejoramiento ramal Tren - Talca-Constitucion</t>
+  </si>
+  <si>
+    <t>Puente Biobio</t>
+  </si>
+  <si>
+    <t>Tren Batuco - Quinta Normal</t>
+  </si>
+  <si>
+    <t>Tren Melipilla - Estacion Central</t>
+  </si>
+  <si>
+    <t>Tren Puerto Montt - Llanquihue</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Plataforma Logistica Ferroportuaria</t>
+  </si>
+  <si>
+    <t>La primera fase de este proyecto corresponde a la modernización del Patio Barrancas ubicado en el costado del terminal portuario de San Antonio y la construcción de desvíos ferroviarios fuera del recinto. La iniciativa, denominada Terminal Intermodal Barrancas permitirá quintuplicar la capacidad de carga movilizada por tren en ese puerto, pasando de 50 mil TEU´s a 250 mil TEU´s por año, con servicios disponibles para todos los concesionarios del puerto. Asimismo, permitirá el tránsito de trenes de mayor longitud, pasando de 400 a 600 metros</t>
+  </si>
+  <si>
+    <t>Nuevo medio de pago</t>
+  </si>
+  <si>
+    <t>Este proyecto considera la modernización del sistema de pago de todos los servicios existentes en el país, correspondientes a las tres filiales con operaciones de pasajeros (EFE Valparaíso, EFE Central y EFE Sur). Contempla el uso de la nueva tarjeta Conecta, válida para cualquiera de los servicios de EFE, con lo que se integra el sistema de cobro, pudiendo utilizarse este medio de pago también en otros sistemas de transporte público. La primera etapa comenzó a implementarse en la Región del Biobío, con la habilitación de la nueva tarjeta, el reemplazo de los validadores, la reparación de torniquetes, la instalación de nuevas máquinas de autoatención en estaciones y el sistema de recarga a través de la aplicación de EFE o por página web. La siguiente etapa correspondió a su habilitación en los servicios de EFE Valparaíso. La tercera fase incorporó el uso de QR, además de tarjeta de crédito y débito (EMV) para pago directo en validadores tanto en Valparaíso como en Concepción. La última etapa, implementada en febrero de 2026 comenzó a operar en el servicio San Fernando- Rancagua-Alameda de EFE Central.</t>
+  </si>
+  <si>
+    <t>Limache - La Calera</t>
+  </si>
+  <si>
+    <t>Este proyecto contempla la ampliación de los servicios del tren Limache Puerto hasta La Calera, incorporando a las comunas de Quillota, La Cruz y La Calera. Considera la construcción de 26 kilómetros de vías dobles para pasajeros y el mejoramiento de la existente para el transporte de carga. En su trazado se proyecta 7 estaciones, pasos vehiculares desnivelados, pasos peatonales desnivelados y 15 nuevos trenes. Actualmente, el proyecto se encuentra en etapa de diseño (ingeniería de detalle) y en tramitación ambiental.</t>
+  </si>
+  <si>
+    <t>Estacion Valencia</t>
+  </si>
+  <si>
+    <t>Cumpliendo con un anhelo transversal de los vecinos de Quilpué, en enero de 2026 se inauguró la Estación Valencia para el servicio de tren Limache-Puerto. En el marco del mismo proyecto, iniciado en 2023, se instaló un paradero de buses para facilitar la conexión a los vecinos de distintos sectores, lo que permite la combinación con el tren en la estación.</t>
+  </si>
+  <si>
+    <t>Nuevos trenes para reforazar servicio Rancagua - Estacion Central</t>
+  </si>
+  <si>
+    <t>Con el propósito de atender la creciente demanda de pasajeros en el servicio Rancagua-Estación Central, EFE realizó durante el mes de diciembre de 2022 la compra de 3 nuevos trenes para reforzar los servicios. Durante 2023, este servicio movilizó un total de 7,1 millones de pasajeros, lo que representa un incremento de 115% en relación con 2021, y de 173% si se compara con 2019, año pre pandemia. Los trenes fueron probados y 2 se encuentran habilitados, poniéndose en servicio en la ruta hasta San Fernando. Gracias a esto, los habitantes de San Fernando pueden usar trenes nuevos después de más de 40 años.</t>
+  </si>
+  <si>
+    <t>Extension de Biotren Coronel - Lota</t>
+  </si>
+  <si>
+    <t>El sistema de transporte en el Gran Concepción ha enfrentado numerosas dificultades a raíz del crecimiento de los sectores habitacionales y la limitada capacidad de traslado por la vialidad existente (Ruta 160) y el deficiente sistema de transporte público (microbuses). A raíz de esta situación, los servicios del Biotren han incrementado considerablemente sus flujos, llegando a 11,7 millones de pasajeros en 2024. De ese total, el 85% corresponde a la Línea 2 que une Coronel y Concepción. Este proyecto, considera la extensión de la Línea 2 hasta Lota, con una inversión de US$ 155 MM, la compra de 6 nuevos trenes y la habilitación de 5 nuevas estaciones (Coronel Sur, Playa Blanca, Cousiño, Chiflón y Lota). Actualmente, el proyecto alcanza un 27% de avance, lo que considera la implementación de medidas de Participación Ciudadana Temprana para el Estudio de Impacto Ambiental.</t>
+  </si>
+  <si>
+    <t>Paradas de Cajon y Padre Las Casas</t>
+  </si>
+  <si>
+    <t>Con el objetivo de mejorar la conectividad de los habitantes de la Región de La Araucanía, se desarrollaron dos proyectos destinados a: Ampliar el servicio Victoria Temuco hacia Padre Las Casas con la instalación de una nueva parada en esa comuna, inaugurada en abril de 2025. En diciembre de 2023, se habilitó una parada en la localidad de Cajón, en la comuna de Vilcún, en un trayecto que realiza el servicio Victoria-Temuco, pero debido a la falta de infraestrutura el tren no se podía detener.</t>
+  </si>
+  <si>
+    <t>Mejoramiento de estaciones Region de O'Higgins</t>
+  </si>
+  <si>
+    <t>Financiacion GORE</t>
+  </si>
+  <si>
+    <t>En el marco del convenio suscrito con la Gobernación Regional de O’Higgins en agosto de 2022 y con el apoyo de la Dirección Regional de Arquitectura del MOP se realizó un primer proceso de licitación para la recuperación arquitectónica de dos primeras estaciones, correspondientes a Requínoa y Rosario, a cargo de la empresa Calfrío, con el financiamiento es del Gobierno Regional.</t>
+  </si>
+  <si>
+    <t>Ampliacion de Capacidad de Biotren</t>
+  </si>
+  <si>
+    <t>La ampliación de capacidad tiene por objetivo aumentar la oferta de servicios ferroviarios en el tramo Concepción-Coronel. El proyecto considera la compra de 10 nuevos trenes, el refuerzo de la alimentación de tracción existente (doble hilo de contacto en catenarias), extensión de los andenes en las 14 estaciones del trazado, como también la modificación de los sistemas ferroviarios, la construcción de un nuevo taller de mantenimiento en Escuadrón y la construcción de una subestación eléctrica rectificadora (SER). El objetivo es duplicar la capacidad de viajes, con la operación de trenes dobles. A través de soluciones modulares en una primera fase (durante primer trimestre de 2027) y de andenes definitivos en una etapa siguiente (hacia 2028), se generará un aumento de oferta de transporte de 40% (en hora punta mañana, durante la primera fase) y de 100% en horas punta mañana y tarde en la segunda fase), minimizando la posibilidad de que los pasajeros queden abajo del tren y deban esperar el siguiente.</t>
+  </si>
+  <si>
+    <t>Adquisicion de 2 nuevos trenes de respaldo para Biotren</t>
+  </si>
+  <si>
+    <t>Para fortalecer la resiliencia de las operaciones de Biotren, se dispuso la compra de dos nuevos trenes destinados a complementar la disponibilidad de material rodante en la Línea 2 de Biotren.</t>
+  </si>
+  <si>
+    <t>Ampliacion de capacidad de operaciones EFE Valparaiso</t>
+  </si>
+  <si>
+    <t>Este proyecto considera la adquisición de 5 nuevos trenes para robustecer el funcionamiento del servicio Limache Puerto, que anualmente mueve más de 20 millones de pasajeros.</t>
+  </si>
+  <si>
+    <t>Adquisicion de 8 locomotoras para tareas de mantenimiento</t>
+  </si>
+  <si>
+    <t>Con el objetivo de reforzar la flota para labores de mantenimiento y traslado de materiales, EFE lleva adelante un proceso de licitación destinado a adquirir 8 locomotoras nuevas, que complementarán la labor desarrollada por las actualmente disponibles que tienen más de 60 años de funcionamiento.</t>
+  </si>
+  <si>
+    <t>Servicio Temuco - Gorbea</t>
+  </si>
+  <si>
+    <t>El nuevo servicio ferroviario entre Temuco y Gorbea considera la rehabilitación completa de la vía férrea, la adquisición de 4 nuevos trenes; la rehabilitación de la estación de Gorbea, además de la construcción de 3 nuevos paraderos (2 en Temuco y 1 en Freire). Asimismo, contempla la habilitación y mejoramiento de 50 pasos peatonales y la automatización de 13 pasos vehiculares. Además, incorpora la ampliación del taller de mantenimiento de Victoria. El tiempo de traslado será de 44 minutos y el estándar de la vía será Clase C para 100 kilómetros/hora. En diciembre de 2025 se iniciaron las obras de rehabilitación de vías, mientars que durante el segundo semestre de 2026 se estima la llegada de cuatro nuevos trenes, actualmente en proceso de fabricación.</t>
+  </si>
+  <si>
+    <t>Construccion Servicio Ferroviario Biotren Hacia el Norte de Concepcion (Biotren a Penco)</t>
+  </si>
+  <si>
+    <t>En factibilidad</t>
+  </si>
+  <si>
+    <t>El proyecto consiste en la extensión en 19,5 km del servicio Biotren desde la comuna de Concepción hacia la comuna de Penco, hasta el sector de Lirquén. Esta extensión se realizará por la actual vía ferroviaria que utilizan los trenes de carga para ir hacia y desde el Puerto Lirquén</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6185,8 +6329,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF525252"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6235,8 +6396,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -6314,8 +6481,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6325,8 +6516,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6512,9 +6704,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="10">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Millares [0]" xfId="9" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Acc_indirectos_20231213" xfId="4" xr:uid="{6B6BC0B8-E100-4969-803B-2B212E7EB7B4}"/>
     <cellStyle name="Normal_Accionista_directo_20231213" xfId="5" xr:uid="{0562E2F8-AB85-4619-8291-99E2ACAF39DA}"/>
@@ -6524,7 +6740,136 @@
     <cellStyle name="Normal_Hoja4" xfId="6" xr:uid="{84239E63-E84F-41D3-AB64-BCC2124F9300}"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF525252"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -15232,7 +15577,7 @@
     <dataField name="Cuenta de Código proyecto" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="40">
+    <format dxfId="48">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -16676,58 +17021,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" headerRowCellStyle="Normal_Hoja1">
-  <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Ruta 5 Tramo Río Bueno - Puerto Montt"/>
-        <filter val="Ruta 5 Tramo Temuco - Río Bueno"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" headerRowCellStyle="Normal_Hoja1">
+  <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AJ128">
-    <sortCondition sortBy="cellColor" ref="C1:C128" dxfId="35"/>
+    <sortCondition sortBy="cellColor" ref="C1:C128" dxfId="43"/>
   </sortState>
   <tableColumns count="35">
-    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="34">
+    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="42">
       <calculatedColumnFormula>MAX($C$2:$C$128)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="33">
+    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="41">
       <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(D2,";")),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="32"/>
+    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="40"/>
     <tableColumn id="1" xr3:uid="{EBDE2C74-BB18-41CD-8BA6-80BB4E8B06B1}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="31" dataCellStyle="Normal_Hoja4"/>
-    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="39" dataCellStyle="Normal_Hoja4"/>
+    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="38"/>
     <tableColumn id="4" xr3:uid="{01B27C31-31AA-4F49-A1FD-C3C1240EB455}" name="Nombre de uso común"/>
-    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="6"/>
-    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="4"/>
-    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="3"/>
-    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="2" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="30"/>
+    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="29"/>
+    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="18"/>
+    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="17"/>
+    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="16"/>
+    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="15"/>
+    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="14"/>
+    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="13"/>
+    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="12"/>
+    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="11"/>
+    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="10" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16738,9 +17076,9 @@
   <autoFilter ref="A1:E398" xr:uid="{0B1BCE94-7066-4FA3-AA56-13A528EB24C5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6692F8DC-A6AC-4EB7-BFE9-9CB212613C31}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{09EFDC4D-986E-43B3-BC94-7B7B41772935}" name="Codigo oferente"/>
-    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{F65361E4-8D72-41BE-9F75-3733E402179A}" name="Adjudicado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -16756,6 +17094,27 @@
     <tableColumn id="3" xr3:uid="{CAC1AC3A-4D5D-4591-9B43-E2C6F9C0F082}" name="Codigo oferente"/>
     <tableColumn id="4" xr3:uid="{BB46A915-2040-4680-9ED2-D4BA9118D4BB}" name="Nombre oferente"/>
     <tableColumn id="5" xr3:uid="{0C1DC836-387C-4D97-9242-473C4DF5811A}" name="Adjudicado"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}" name="Tabla5" displayName="Tabla5" ref="A1:H22" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H22" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{1EA8F6C1-92AF-464C-97F8-5259DBA7CBB5}" name="max" dataDxfId="7">
+      <calculatedColumnFormula>MAX($B$2:$B$128)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{33793EA3-34D7-4D6D-B86D-3F250842C10A}" name="aux" dataDxfId="6">
+      <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{14343C55-2461-432C-9954-29952162B76E}" name="Shapes"/>
+    <tableColumn id="4" xr3:uid="{0A185E16-2B61-4FF8-AF73-88336466F284}" name="Proyecto" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{AFB4B37C-C7FF-4D77-AB2A-762A7D41A8ED}" name="Institucion mandante" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{D863FC92-BAB3-47C2-BB80-F22D29F3D864}" name="Fuente  de inf" dataDxfId="3" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{D3486ADD-FCAB-467D-B0EB-251EEB3E245B}" name="Inversion (USD) " dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17470,7 +17829,7 @@
   <dimension ref="A1:AK128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
     <col min="5" max="5" width="17.109375" customWidth="1"/>
     <col min="6" max="6" width="24.5546875" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
@@ -17618,7 +17977,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <f t="shared" ref="B2:B33" si="0">MAX($C$2:$C$128)</f>
         <v>189</v>
@@ -17729,7 +18088,7 @@
         <v>EIMQ1</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -17842,7 +18201,7 @@
         <v>PBCH1</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="130.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -17909,7 +18268,7 @@
         <v>PDRC1</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1891</v>
       </c>
@@ -18025,7 +18384,7 @@
         <v>160R1</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1892</v>
       </c>
@@ -18141,7 +18500,7 @@
         <v>1AVO1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -18254,7 +18613,7 @@
         <v>21RG1</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -18367,7 +18726,7 @@
         <v>2AVO1</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1893</v>
       </c>
@@ -18483,7 +18842,7 @@
         <v>43RU1</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1894</v>
       </c>
@@ -18599,7 +18958,7 @@
         <v>60GR1</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1895</v>
       </c>
@@ -18715,7 +19074,7 @@
         <v>60RU1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -18828,7 +19187,7 @@
         <v>66RF1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1896</v>
       </c>
@@ -18944,7 +19303,7 @@
         <v>66RF2</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -19057,7 +19416,7 @@
         <v>67CV1</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1897</v>
       </c>
@@ -19173,7 +19532,7 @@
         <v>ACIQ1</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1898</v>
       </c>
@@ -19289,7 +19648,7 @@
         <v>ACNO1</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1899</v>
       </c>
@@ -19405,7 +19764,7 @@
         <v>ANCO1</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -19518,7 +19877,7 @@
         <v>AAMB1</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -19631,7 +19990,7 @@
         <v>AAMB2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="244.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1901</v>
       </c>
@@ -19747,7 +20106,7 @@
         <v>ACHA1</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1900</v>
       </c>
@@ -19863,7 +20222,7 @@
         <v>ACHA2</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -19976,7 +20335,7 @@
         <v>ACIP1</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20089,7 +20448,7 @@
         <v>ACIP2</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20202,7 +20561,7 @@
         <v>ANCO2</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20315,7 +20674,7 @@
         <v>ACMA1</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20428,7 +20787,7 @@
         <v>ACMA2</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20541,7 +20900,7 @@
         <v>AURA1</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1902</v>
       </c>
@@ -20657,7 +21016,7 @@
         <v>ACSU1</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1903</v>
       </c>
@@ -20773,7 +21132,7 @@
         <v>ACSU2</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -20886,7 +21245,7 @@
         <v>ADAI1</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1905</v>
       </c>
@@ -21002,7 +21361,7 @@
         <v>ADAI2</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <f t="shared" si="0"/>
         <v>189</v>
@@ -21115,7 +21474,7 @@
         <v>ADAI3</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1904</v>
       </c>
@@ -21231,7 +21590,7 @@
         <v>ADAI4</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="147.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" ht="147.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <f t="shared" ref="B34:B65" si="2">MAX($C$2:$C$128)</f>
         <v>189</v>
@@ -21344,7 +21703,7 @@
         <v>ALFS1</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -21457,7 +21816,7 @@
         <v>ALFS2</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -21570,7 +21929,7 @@
         <v>ALFS3</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1906</v>
       </c>
@@ -21686,7 +22045,7 @@
         <v>ALOA1</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1907</v>
       </c>
@@ -21802,7 +22161,7 @@
         <v>ALOA2</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -21915,7 +22274,7 @@
         <v>ALOA3</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22028,7 +22387,7 @@
         <v>AVAM1</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="180" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22141,7 +22500,7 @@
         <v>AVAM2</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22254,7 +22613,7 @@
         <v>ARAT1</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22365,7 +22724,7 @@
         <v>ARNO1</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22478,7 +22837,7 @@
         <v>ATEP1</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22591,7 +22950,7 @@
         <v>ATEP2</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="168.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22704,7 +23063,7 @@
         <v>ATEP3</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22817,7 +23176,7 @@
         <v>ATEP4</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -22930,7 +23289,7 @@
         <v>AVAM3</v>
       </c>
     </row>
-    <row r="49" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23043,7 +23402,7 @@
         <v>AVES1</v>
       </c>
     </row>
-    <row r="50" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23156,7 +23515,7 @@
         <v>AVNP1</v>
       </c>
     </row>
-    <row r="51" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23269,7 +23628,7 @@
         <v>CDMA1</v>
       </c>
     </row>
-    <row r="52" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23382,7 +23741,7 @@
         <v>CHCO1</v>
       </c>
     </row>
-    <row r="53" spans="2:37" ht="242.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:37" ht="242.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23495,7 +23854,7 @@
         <v>CHCO2</v>
       </c>
     </row>
-    <row r="54" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23608,7 +23967,7 @@
         <v>CNPU1</v>
       </c>
     </row>
-    <row r="55" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23721,7 +24080,7 @@
         <v>CFLL1</v>
       </c>
     </row>
-    <row r="56" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23834,7 +24193,7 @@
         <v>CNPU2</v>
       </c>
     </row>
-    <row r="57" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -23947,7 +24306,7 @@
         <v>COCA1</v>
       </c>
     </row>
-    <row r="58" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24060,7 +24419,7 @@
         <v>CMVR1</v>
       </c>
     </row>
-    <row r="59" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24173,7 +24532,7 @@
         <v>COTE1</v>
       </c>
     </row>
-    <row r="60" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24286,7 +24645,7 @@
         <v>ISVV1</v>
       </c>
     </row>
-    <row r="61" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24397,7 +24756,7 @@
         <v>ISVV2</v>
       </c>
     </row>
-    <row r="62" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24510,7 +24869,7 @@
         <v>LVLS1</v>
       </c>
     </row>
-    <row r="63" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24623,7 +24982,7 @@
         <v>CSJS1</v>
       </c>
     </row>
-    <row r="64" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24736,7 +25095,7 @@
         <v>CTSR1</v>
       </c>
     </row>
-    <row r="65" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -24849,7 +25208,7 @@
         <v>CVSR1</v>
       </c>
     </row>
-    <row r="66" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1">
         <f t="shared" ref="B66:B97" si="4">MAX($C$2:$C$128)</f>
         <v>189</v>
@@ -24962,7 +25321,7 @@
         <v>ECVI1</v>
       </c>
     </row>
-    <row r="67" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25075,7 +25434,7 @@
         <v>EEBA1</v>
       </c>
     </row>
-    <row r="68" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25188,7 +25547,7 @@
         <v>EIMC1</v>
       </c>
     </row>
-    <row r="69" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25301,7 +25660,7 @@
         <v>ELPA1</v>
       </c>
     </row>
-    <row r="70" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25412,7 +25771,7 @@
         <v>EPCO1</v>
       </c>
     </row>
-    <row r="71" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25525,7 +25884,7 @@
         <v>EPUN1</v>
       </c>
     </row>
-    <row r="72" spans="2:37" ht="150" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:37" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25638,7 +25997,7 @@
         <v>ETPO1</v>
       </c>
     </row>
-    <row r="73" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25751,7 +26110,7 @@
         <v>ETTT1</v>
       </c>
     </row>
-    <row r="74" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25864,7 +26223,7 @@
         <v>HBUP1</v>
       </c>
     </row>
-    <row r="75" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -25977,7 +26336,7 @@
         <v>HINN1</v>
       </c>
     </row>
-    <row r="76" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26090,7 +26449,7 @@
         <v>HRBB1</v>
       </c>
     </row>
-    <row r="77" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26203,7 +26562,7 @@
         <v>HRMA1</v>
       </c>
     </row>
-    <row r="78" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26314,7 +26673,7 @@
         <v>HROG1</v>
       </c>
     </row>
-    <row r="79" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26427,7 +26786,7 @@
         <v>HRQQ1</v>
       </c>
     </row>
-    <row r="80" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26540,7 +26899,7 @@
         <v>HRQS1</v>
       </c>
     </row>
-    <row r="81" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26653,7 +27012,7 @@
         <v>HRRL1</v>
       </c>
     </row>
-    <row r="82" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26766,7 +27125,7 @@
         <v>HSAN1</v>
       </c>
     </row>
-    <row r="83" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26879,7 +27238,7 @@
         <v>HSFB1</v>
       </c>
     </row>
-    <row r="84" spans="1:37" ht="223.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:37" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -26992,7 +27351,7 @@
         <v>HSMF1</v>
       </c>
     </row>
-    <row r="85" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27105,7 +27464,7 @@
         <v>HSSG1</v>
       </c>
     </row>
-    <row r="86" spans="1:37" ht="148.94999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:37" ht="148.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27218,7 +27577,7 @@
         <v>INAC1</v>
       </c>
     </row>
-    <row r="87" spans="1:37" ht="148.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:37" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27331,7 +27690,7 @@
         <v>LVLS2</v>
       </c>
     </row>
-    <row r="88" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1908</v>
       </c>
@@ -27447,7 +27806,7 @@
         <v>NPIB1</v>
       </c>
     </row>
-    <row r="89" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27560,7 +27919,7 @@
         <v>ORSS1</v>
       </c>
     </row>
-    <row r="90" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27673,7 +28032,7 @@
         <v>NARA1</v>
       </c>
     </row>
-    <row r="91" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -27784,7 +28143,7 @@
         <v>NARA2</v>
       </c>
     </row>
-    <row r="92" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -28071,7 +28430,7 @@
         <v>RBPM2</v>
       </c>
     </row>
-    <row r="95" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -28184,7 +28543,7 @@
         <v>PCIS1</v>
       </c>
     </row>
-    <row r="96" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -28297,7 +28656,7 @@
         <v>RITP1</v>
       </c>
     </row>
-    <row r="97" spans="2:37" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:37" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B97" s="1">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -28410,7 +28769,7 @@
         <v>PP1G1</v>
       </c>
     </row>
-    <row r="98" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1">
         <f t="shared" ref="B98:B128" si="6">MAX($C$2:$C$128)</f>
         <v>189</v>
@@ -28523,7 +28882,7 @@
         <v>PP2G1</v>
       </c>
     </row>
-    <row r="99" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -28636,7 +28995,7 @@
         <v>PP2G2</v>
       </c>
     </row>
-    <row r="100" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -28749,7 +29108,7 @@
         <v>PP3G1</v>
       </c>
     </row>
-    <row r="101" spans="2:37" ht="168.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -28860,7 +29219,7 @@
         <v>PP4T1</v>
       </c>
     </row>
-    <row r="102" spans="2:37" ht="131.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:37" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -28973,7 +29332,7 @@
         <v>PTLA1</v>
       </c>
     </row>
-    <row r="103" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29086,7 +29445,7 @@
         <v>RAUS1</v>
       </c>
     </row>
-    <row r="104" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29199,7 +29558,7 @@
         <v>RLOA1</v>
       </c>
     </row>
-    <row r="105" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29310,7 +29669,7 @@
         <v>RLOA2</v>
       </c>
     </row>
-    <row r="106" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29423,7 +29782,7 @@
         <v>RNAH1</v>
       </c>
     </row>
-    <row r="107" spans="2:37" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:37" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29486,7 +29845,7 @@
         <v>RPMO1</v>
       </c>
     </row>
-    <row r="108" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29545,7 +29904,7 @@
         <v>RTCC</v>
       </c>
     </row>
-    <row r="109" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29658,7 +30017,7 @@
         <v>RVLC1</v>
       </c>
     </row>
-    <row r="110" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29771,7 +30130,7 @@
         <v>SALV1</v>
       </c>
     </row>
-    <row r="111" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29882,7 +30241,7 @@
         <v>SALV2</v>
       </c>
     </row>
-    <row r="112" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -29995,7 +30354,7 @@
         <v>SASA1</v>
       </c>
     </row>
-    <row r="113" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30108,7 +30467,7 @@
         <v>SASA2</v>
       </c>
     </row>
-    <row r="114" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30221,7 +30580,7 @@
         <v>SATA1</v>
       </c>
     </row>
-    <row r="115" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30334,7 +30693,7 @@
         <v>SCLA1</v>
       </c>
     </row>
-    <row r="116" spans="1:37" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:37" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30447,7 +30806,7 @@
         <v>SNSS1</v>
       </c>
     </row>
-    <row r="117" spans="1:37" ht="155.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:37" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30560,7 +30919,7 @@
         <v>SOPN1</v>
       </c>
     </row>
-    <row r="118" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30673,7 +31032,7 @@
         <v>TACH1</v>
       </c>
     </row>
-    <row r="119" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30786,7 +31145,7 @@
         <v>TACH2</v>
       </c>
     </row>
-    <row r="120" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -30899,7 +31258,7 @@
         <v>TELB1</v>
       </c>
     </row>
-    <row r="121" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1890</v>
       </c>
@@ -31015,7 +31374,7 @@
         <v>TEME1</v>
       </c>
     </row>
-    <row r="122" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -31352,7 +31711,7 @@
         <v>TERB2</v>
       </c>
     </row>
-    <row r="125" spans="1:37" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:37" ht="201.6" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -31465,7 +31824,7 @@
         <v>VALS1</v>
       </c>
     </row>
-    <row r="126" spans="1:37" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:37" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -31578,7 +31937,7 @@
         <v>VAME1</v>
       </c>
     </row>
-    <row r="127" spans="1:37" ht="125.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:37" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -31691,7 +32050,7 @@
         <v>VCAL1</v>
       </c>
     </row>
-    <row r="128" spans="1:37" ht="259.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:37" ht="259.2" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
         <f t="shared" si="6"/>
         <v>189</v>
@@ -31838,6 +32197,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BB4B64-B9F4-4456-809A-D79D9348ED16}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB24780-DA24-443E-8AC7-974CDFAF53A5}">
   <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -38623,7 +38991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CAEB3E-9B0B-46C0-A51A-397ED4B2A125}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -38677,7 +39045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A027213-CBDF-4546-AB50-6C5C843A4721}">
   <dimension ref="A3:B284"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41223,7 +41591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF98742-97F0-49C5-9E66-7A675B4A5A19}">
   <dimension ref="A3:A6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41251,4 +41619,559 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277D185D-4316-48AF-BD8E-255CDB7079DD}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D1" s="86" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1" s="87" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1" s="87" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="83">
+        <f>MAX($B$2:$B$128)</f>
+        <v>10</v>
+      </c>
+      <c r="B2" s="75" cm="1">
+        <f t="array" ref="B2">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</f>
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F2" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G2" s="78">
+        <v>811000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="84">
+        <f t="shared" ref="A3:A22" si="0">MAX($B$2:$B$128)</f>
+        <v>10</v>
+      </c>
+      <c r="B3" s="85" cm="1">
+        <f t="array" ref="B3">IFERROR(MAX(--_xlfn.TEXTSPLIT(C3,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E3" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F3" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G3" s="79">
+        <v>160000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B4" s="75" cm="1">
+        <f t="array" ref="B4">IFERROR(MAX(--_xlfn.TEXTSPLIT(C4,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E4" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G4" s="79">
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B5" s="85" cm="1">
+        <f t="array" ref="B5">IFERROR(MAX(--_xlfn.TEXTSPLIT(C5,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E5" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G5" s="79">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B6" s="75" cm="1">
+        <f t="array" ref="B6">IFERROR(MAX(--_xlfn.TEXTSPLIT(C6,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E6" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F6" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G6" s="79">
+        <v>950000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B7" s="85" cm="1">
+        <f t="array" ref="B7">IFERROR(MAX(--_xlfn.TEXTSPLIT(C7,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E7" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F7" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G7" s="79">
+        <v>1877000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B8" s="75" cm="1">
+        <f t="array" ref="B8">IFERROR(MAX(--_xlfn.TEXTSPLIT(C8,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E8" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F8" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B9" s="85" cm="1">
+        <f t="array" ref="B9">IFERROR(MAX(--_xlfn.TEXTSPLIT(C9,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F9" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G9" s="79">
+        <v>79000000</v>
+      </c>
+      <c r="H9" s="80" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="75" cm="1">
+        <f t="array" ref="B10">IFERROR(MAX(--_xlfn.TEXTSPLIT(C10,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G10" s="79">
+        <v>8000000</v>
+      </c>
+      <c r="H10" s="81" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="85" cm="1">
+        <f t="array" ref="B11">IFERROR(MAX(--_xlfn.TEXTSPLIT(C11,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F11" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G11" s="79">
+        <v>880000000</v>
+      </c>
+      <c r="H11" s="80" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="75" cm="1">
+        <f t="array" ref="B12">IFERROR(MAX(--_xlfn.TEXTSPLIT(C12,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G12" s="79">
+        <v>22600000</v>
+      </c>
+      <c r="H12" s="80" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="85" cm="1">
+        <f t="array" ref="B13">IFERROR(MAX(--_xlfn.TEXTSPLIT(C13,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G13" s="79">
+        <v>17600000</v>
+      </c>
+      <c r="H13" s="80" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="75" cm="1">
+        <f t="array" ref="B14">IFERROR(MAX(--_xlfn.TEXTSPLIT(C14,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F14" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G14" s="79">
+        <v>155000000</v>
+      </c>
+      <c r="H14" s="81" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B15" s="85" cm="1">
+        <f t="array" ref="B15">IFERROR(MAX(--_xlfn.TEXTSPLIT(C15,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E15" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F15" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G15" s="79">
+        <v>700000</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="75" cm="1">
+        <f t="array" ref="B16">IFERROR(MAX(--_xlfn.TEXTSPLIT(C16,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E16" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F16" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H16" s="80" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="85" cm="1">
+        <f t="array" ref="B17">IFERROR(MAX(--_xlfn.TEXTSPLIT(C17,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E17" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F17" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G17" s="79">
+        <v>276000000</v>
+      </c>
+      <c r="H17" s="80" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B18" s="75" cm="1">
+        <f t="array" ref="B18">IFERROR(MAX(--_xlfn.TEXTSPLIT(C18,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G18" s="79">
+        <v>12000000</v>
+      </c>
+      <c r="H18" s="80" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B19" s="85" cm="1">
+        <f t="array" ref="B19">IFERROR(MAX(--_xlfn.TEXTSPLIT(C19,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E19" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F19" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G19" s="79">
+        <v>35000000</v>
+      </c>
+      <c r="H19" s="80" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B20" s="85" cm="1">
+        <f t="array" ref="B20">IFERROR(MAX(--_xlfn.TEXTSPLIT(C20,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G20" s="79">
+        <v>32000000</v>
+      </c>
+      <c r="H20" s="80" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B21" s="85" cm="1">
+        <f t="array" ref="B21">IFERROR(MAX(--_xlfn.TEXTSPLIT(C21,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E21" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F21" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G21" s="79">
+        <v>212000000</v>
+      </c>
+      <c r="H21" s="80" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="83">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B22" s="75" cm="1">
+        <f t="array" ref="B22">IFERROR(MAX(--_xlfn.TEXTSPLIT(C22,";")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E22" s="76" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G22" s="82" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H22" s="80" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/CATLEC.xlsx
+++ b/CATLEC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edison\Desktop\CATLEC\Codigo CATLEC - backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5572B8D9-8510-4866-869A-48C8C3433842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70DE4E5-7DE6-4238-A58F-309C0DF517BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4766" uniqueCount="1983">
   <si>
     <t>Código proyecto</t>
   </si>
@@ -6130,12 +6130,6 @@
     <t>Este proyecto considera la modernización del sistema de pago de todos los servicios existentes en el país, correspondientes a las tres filiales con operaciones de pasajeros (EFE Valparaíso, EFE Central y EFE Sur). Contempla el uso de la nueva tarjeta Conecta, válida para cualquiera de los servicios de EFE, con lo que se integra el sistema de cobro, pudiendo utilizarse este medio de pago también en otros sistemas de transporte público. La primera etapa comenzó a implementarse en la Región del Biobío, con la habilitación de la nueva tarjeta, el reemplazo de los validadores, la reparación de torniquetes, la instalación de nuevas máquinas de autoatención en estaciones y el sistema de recarga a través de la aplicación de EFE o por página web. La siguiente etapa correspondió a su habilitación en los servicios de EFE Valparaíso. La tercera fase incorporó el uso de QR, además de tarjeta de crédito y débito (EMV) para pago directo en validadores tanto en Valparaíso como en Concepción. La última etapa, implementada en febrero de 2026 comenzó a operar en el servicio San Fernando- Rancagua-Alameda de EFE Central.</t>
   </si>
   <si>
-    <t>Limache - La Calera</t>
-  </si>
-  <si>
-    <t>Este proyecto contempla la ampliación de los servicios del tren Limache Puerto hasta La Calera, incorporando a las comunas de Quillota, La Cruz y La Calera. Considera la construcción de 26 kilómetros de vías dobles para pasajeros y el mejoramiento de la existente para el transporte de carga. En su trazado se proyecta 7 estaciones, pasos vehiculares desnivelados, pasos peatonales desnivelados y 15 nuevos trenes. Actualmente, el proyecto se encuentra en etapa de diseño (ingeniería de detalle) y en tramitación ambiental.</t>
-  </si>
-  <si>
     <t>Estacion Valencia</t>
   </si>
   <si>
@@ -6214,12 +6208,6 @@
     <t>1;2;3</t>
   </si>
   <si>
-    <t>4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22</t>
-  </si>
-  <si>
-    <t>23;24;9</t>
-  </si>
-  <si>
     <t>25;26</t>
   </si>
   <si>
@@ -6239,6 +6227,77 @@
   </si>
   <si>
     <t>region</t>
+  </si>
+  <si>
+    <t>38;45</t>
+  </si>
+  <si>
+    <t>Ñuble;Maule;O'Higgins;Metropolitana</t>
+  </si>
+  <si>
+    <t>Biobio</t>
+  </si>
+  <si>
+    <t>Nacional</t>
+  </si>
+  <si>
+    <t>O'Higgins;Metropolitana</t>
+  </si>
+  <si>
+    <t>O'Higgins</t>
+  </si>
+  <si>
+    <t>47;48;49;50;51;52</t>
+  </si>
+  <si>
+    <t>42;53</t>
+  </si>
+  <si>
+    <t>23;9;54</t>
+  </si>
+  <si>
+    <t>56;53</t>
+  </si>
+  <si>
+    <t>57;58</t>
+  </si>
+  <si>
+    <t>4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;46;59;60</t>
+  </si>
+  <si>
+    <t>55;11;14;15;16;17;18;19;20;21;22;46;60</t>
+  </si>
+  <si>
+    <t>El proyecto de extensión ferroviaria desde Limache a Quillota, La Cruz, La Calera, representa la inversión ferroviaria más importante en la Región de Valparaíso, con una inversión estimada de 811 millones de dólares. El trazado contempla 26 kilómetros de vías -doble vía exclusiva para de pasajeros y una vía para carga-, 7 estaciones en total (actual estación Limache, 5 estaciones nuevas y recuperación de la antigua Estación La Calera) , pasos vehiculares y peatonales desnivelados, así como la adquisición de 15 nuevos trenes. Todas las estaciones consideran estándares de accesibilidad universal y eficiencia energética. El desarrollo de esta infraestructura permitirá extender las ventajas en conectividad del tren a una población beneficiaria de 1.118.449 personas. En concreto, la operación del servicio permitirá importantes ahorros en tiempos de viaje y mayor seguridad en los desplazamientos de los pasajeros. Al mismo tiempo reportará impactos positivos para toda la comunidad gracias a la reducción de emisiones contaminantes, mejoramiento de la seguridad de los cruces vehiculares y peatonales, y disminución de la congestión vial, entre otros factores que contribuyen a tener mejores ciudades para las personas.</t>
+  </si>
+  <si>
+    <t>El proyecto, que considera una inversión que alcanza los 40 millones de dólares, incluye cuatro áreas de trabajo: adquisición de nuevos buscarriles; construcción de un nuevo centro de mantenimiento para el material rodante; rehabilitación de la vía y reparación y recuperación de estaciones y paraderos, ámbito en el que EFE Trenes de Chile cuenta con el apoyo del Gobierno regional del Maule. </t>
+  </si>
+  <si>
+    <t>El proyecto consideró la construcción de un viaducto de 1,8 kilómetroscondos vías electrificadas para uso mixto de trenes de carga y pasajeros. La estructura se fundó sobre pilotes de entre 28 y 46 metros de profundidad e incorpora sistemas de evacuación de aguas lluvia, iluminación, confinamiento de la faja vía y diseño arquitectónico. También incluye pantallas acústicas a la salida del túnel, mejoras paisajísticas y el rediseño del patio de maniobras de la boca sur. Asimismo, se construyó un nuevo túnel en el Cerro Chepe, excavado en roca, de 325 metros de longitud y con dos vías férreas, que además contempla obras de paisajismo en sus accesos.</t>
+  </si>
+  <si>
+    <t>El Tren Santiago – Batuco es una de las iniciativas más emblemáticas del Plan Nacional de Desarrollo Ferroviario, con una inversión total estimada de US$ 950 millones, que busca mejorar la conectividad del transporte público en el norponiente de la Región Metropolitana. El proyecto permitirá fortalecer la movilidad entre las comunas de Lampa, Quilicura, Renca, Quinta Normal y Santiago, beneficiando directamente a cerca de un millón de habitantes y contribuyendo al desarrollo de un sistema de transporte público moderno, seguro y sustentable. De las ocho estaciones contempladas, seis se construyen en superficie, las que estarán ubicadas en las comunas de Renca, Quilicura y Lampa, cumpliendo con altos estándares de accesibilidad universal y seguridad. La conectividad que ofrece el proyecto permitirá una importante integración con el sistema de transporte público de Santiago, conectando los servicios con las líneas 3, 5 y 7 del Metro de Santiago.
+La ejecución del proyecto destaca, además, la construcción de 7 puentes ferroviarios, incluido el Puente Mapocho, 12 pasos peatonales desnivelados, asegurando cruces seguros; además de pasos vehiculares desnivelados (3 superiores y 2 inferiores).</t>
+  </si>
+  <si>
+    <t>La iniciativa, que permitirá ahorros de hasta más de 2 horas diarias de tiempo de viaje, considera 11 estaciones en un trayecto de 61 kilómetros de extensión, con tres vías hasta Malloco (dos de pasajeros y una de carga) y dos hasta Melipilla (una de pasajeros y una de carga), junto con conexión con líneas 1 y 6 de Metro. Se estima que el nuevo trazado tendrá una demanda aproximada de 57 millones de pasajeros por año para un área de influencia de más de un millón 100 mil habitantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tren Llanquihue – Puerto Montt, inaugurado el 29 de abril del 2025 es un proyecto de cercanías 30/30, que tiene como objetivo habilitar un servicio ferroviario piloto con la infraestructura existente y abarca una longitud de 27 kilómetros y que une a tres comunas de la Región de Los Lagos, beneficiando a 308.000 habitantes. El proyecto contempla la utilización de dos trenes regulares y cuatro detenciones, en las localidades de Llanquihue, Puerto Varas, Alerce y La Paloma, permitiendo realizar el trayecto de punta a punta en tan sólo 40 minutos. A su vez, contempla intermodalidad que permite llegar hasta el centro cívico de Puerto Montt a través de una tarifa integrada.
+</t>
+  </si>
+  <si>
+    <t>EFE Sur</t>
+  </si>
+  <si>
+    <t>EFE Central</t>
+  </si>
+  <si>
+    <t>EFE Valparaíso</t>
+  </si>
+  <si>
+    <t>Filial</t>
   </si>
 </sst>
 </file>
@@ -6538,7 +6597,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6747,6 +6806,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -6760,9 +6822,9 @@
     <cellStyle name="Normal_Hoja4" xfId="6" xr:uid="{84239E63-E84F-41D3-AB64-BCC2124F9300}"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="51">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -6805,6 +6867,9 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -12104,7 +12169,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09FD9B7D-78F1-439B-BBB9-5FF07678024F}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09FD9B7D-78F1-439B-BBB9-5FF07678024F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField dataField="1" showAll="0"/>
@@ -12253,7 +12318,7 @@
     <dataField name="Cuenta de Código proyecto" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="49">
+    <format dxfId="50">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -12276,51 +12341,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" headerRowCellStyle="Normal_Hoja1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" headerRowCellStyle="Normal_Hoja1">
   <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AJ128">
-    <sortCondition sortBy="cellColor" ref="C1:C128" dxfId="44"/>
+    <sortCondition sortBy="cellColor" ref="C1:C128" dxfId="45"/>
   </sortState>
   <tableColumns count="35">
-    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="43">
+    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="44">
       <calculatedColumnFormula>MAX($C$2:$C$128)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="42">
+    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="43">
       <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(D2,";")),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="41"/>
+    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="42"/>
     <tableColumn id="1" xr3:uid="{EBDE2C74-BB18-41CD-8BA6-80BB4E8B06B1}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="40" dataCellStyle="Normal_Hoja4"/>
-    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="41" dataCellStyle="Normal_Hoja4"/>
+    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="40"/>
     <tableColumn id="4" xr3:uid="{01B27C31-31AA-4F49-A1FD-C3C1240EB455}" name="Nombre de uso común"/>
-    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="37"/>
-    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="34"/>
-    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="33"/>
-    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="30"/>
-    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="29"/>
-    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="28"/>
-    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="27"/>
-    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="23"/>
-    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="21"/>
-    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="20"/>
-    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="19"/>
-    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="18"/>
-    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="16"/>
-    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="15"/>
-    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="14"/>
-    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="13"/>
-    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="11" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="21"/>
+    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="20"/>
+    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="18"/>
+    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="17"/>
+    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="16"/>
+    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="14"/>
+    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="13"/>
+    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="12" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12331,9 +12396,9 @@
   <autoFilter ref="A1:E398" xr:uid="{0B1BCE94-7066-4FA3-AA56-13A528EB24C5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6692F8DC-A6AC-4EB7-BFE9-9CB212613C31}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{09EFDC4D-986E-43B3-BC94-7B7B41772935}" name="Codigo oferente"/>
-    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="10"/>
     <tableColumn id="5" xr3:uid="{F65361E4-8D72-41BE-9F75-3733E402179A}" name="Adjudicado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12341,21 +12406,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}" name="Tabla5" displayName="Tabla5" ref="A1:I22" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:I22" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1EA8F6C1-92AF-464C-97F8-5259DBA7CBB5}" name="max" dataDxfId="7">
-      <calculatedColumnFormula>MAX($B$2:$B$128)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}" name="Tabla5" displayName="Tabla5" ref="A1:J21" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:J21" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{1EA8F6C1-92AF-464C-97F8-5259DBA7CBB5}" name="max" dataDxfId="8">
+      <calculatedColumnFormula>MAX($B$2:$B$127)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33793EA3-34D7-4D6D-B86D-3F250842C10A}" name="aux" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{33793EA3-34D7-4D6D-B86D-3F250842C10A}" name="aux" dataDxfId="7">
       <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{14343C55-2461-432C-9954-29952162B76E}" name="Shapes"/>
-    <tableColumn id="4" xr3:uid="{0A185E16-2B61-4FF8-AF73-88336466F284}" name="Proyecto" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{7C61B78F-F4DD-4F80-8D4D-AABD3B55036C}" name="region" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{0A185E16-2B61-4FF8-AF73-88336466F284}" name="Proyecto" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{7C61B78F-F4DD-4F80-8D4D-AABD3B55036C}" name="region" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{AFB4B37C-C7FF-4D77-AB2A-762A7D41A8ED}" name="Institucion mandante" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{D863FC92-BAB3-47C2-BB80-F22D29F3D864}" name="Fuente  de inf" dataDxfId="3" dataCellStyle="Hipervínculo"/>
     <tableColumn id="7" xr3:uid="{D3486ADD-FCAB-467D-B0EB-251EEB3E245B}" name="Inversion (USD) " dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{B4EFD4AE-28EB-449A-AD8D-58C9B7719A54}" name="Filial" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -34256,7 +34322,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277D185D-4316-48AF-BD8E-255CDB7079DD}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
@@ -34265,12 +34331,13 @@
     <col min="6" max="6" width="21.109375" customWidth="1"/>
     <col min="7" max="7" width="28.21875" customWidth="1"/>
     <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B1" t="s">
         <v>1743</v>
@@ -34282,7 +34349,7 @@
         <v>1908</v>
       </c>
       <c r="E1" s="86" t="s">
-        <v>1963</v>
+        <v>1959</v>
       </c>
       <c r="F1" s="87" t="s">
         <v>1909</v>
@@ -34294,20 +34361,23 @@
         <v>1911</v>
       </c>
       <c r="I1" s="86" t="s">
+        <v>1982</v>
+      </c>
+      <c r="J1" s="86" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="83">
-        <f>MAX($B$2:$B$128)</f>
-        <v>44</v>
+        <f t="shared" ref="A2:A21" si="0">MAX($B$2:$B$127)</f>
+        <v>60</v>
       </c>
       <c r="B2" s="75" cm="1">
         <f t="array" ref="B2">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</f>
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>1913</v>
@@ -34324,23 +34394,31 @@
       <c r="H2" s="78">
         <v>811000000</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="78" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J2" s="80" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="84">
-        <f t="shared" ref="A3:A22" si="0">MAX($B$2:$B$128)</f>
-        <v>44</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="B3" s="85" cm="1">
         <f t="array" ref="B3">IFERROR(MAX(--_xlfn.TEXTSPLIT(C3,";")),0)</f>
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>1955</v>
+        <v>1971</v>
       </c>
       <c r="D3" s="39" t="s">
         <v>1916</v>
       </c>
-      <c r="E3" s="39"/>
+      <c r="E3" s="39" t="s">
+        <v>1961</v>
+      </c>
       <c r="F3" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34350,23 +34428,28 @@
       <c r="H3" s="79">
         <v>160000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="79" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B4" s="75" cm="1">
         <f t="array" ref="B4">IFERROR(MAX(--_xlfn.TEXTSPLIT(C4,";")),0)</f>
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>1956</v>
+        <v>1968</v>
       </c>
       <c r="D4" s="39" t="s">
         <v>1917</v>
       </c>
-      <c r="E4" s="39"/>
+      <c r="E4" s="39" t="s">
+        <v>866</v>
+      </c>
       <c r="F4" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34376,23 +34459,31 @@
       <c r="H4" s="79">
         <v>40000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="79" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J4" s="80" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B5" s="85" cm="1">
         <f t="array" ref="B5">IFERROR(MAX(--_xlfn.TEXTSPLIT(C5,";")),0)</f>
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="D5" s="39" t="s">
         <v>1918</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="39" t="s">
+        <v>1962</v>
+      </c>
       <c r="F5" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34402,23 +34493,31 @@
       <c r="H5" s="79">
         <v>3000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J5" s="80" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B6" s="75" cm="1">
         <f t="array" ref="B6">IFERROR(MAX(--_xlfn.TEXTSPLIT(C6,";")),0)</f>
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1958</v>
+        <v>1954</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>1919</v>
       </c>
-      <c r="E6" s="39"/>
+      <c r="E6" s="39" t="s">
+        <v>912</v>
+      </c>
       <c r="F6" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34428,23 +34527,31 @@
       <c r="H6" s="79">
         <v>950000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="79" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J6" s="89" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B7" s="85" cm="1">
         <f t="array" ref="B7">IFERROR(MAX(--_xlfn.TEXTSPLIT(C7,";")),0)</f>
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>1959</v>
+        <v>1955</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>1920</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="39" t="s">
+        <v>912</v>
+      </c>
       <c r="F7" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34454,11 +34561,17 @@
       <c r="H7" s="79">
         <v>1877000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="79" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J7" s="80" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B8" s="75" cm="1">
         <f t="array" ref="B8">IFERROR(MAX(--_xlfn.TEXTSPLIT(C8,";")),0)</f>
@@ -34470,7 +34583,9 @@
       <c r="D8" s="39" t="s">
         <v>1921</v>
       </c>
-      <c r="E8" s="39"/>
+      <c r="E8" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="F8" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34480,11 +34595,17 @@
       <c r="H8" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J8" s="90" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B9" s="85" cm="1">
         <f t="array" ref="B9">IFERROR(MAX(--_xlfn.TEXTSPLIT(C9,";")),0)</f>
@@ -34496,7 +34617,9 @@
       <c r="D9" s="39" t="s">
         <v>1923</v>
       </c>
-      <c r="E9" s="39"/>
+      <c r="E9" s="39" t="s">
+        <v>37</v>
+      </c>
       <c r="F9" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34506,14 +34629,17 @@
       <c r="H9" s="79">
         <v>79000000</v>
       </c>
-      <c r="I9" s="80" t="s">
+      <c r="I9" s="79" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J9" s="80" t="s">
         <v>1924</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B10" s="75" cm="1">
         <f t="array" ref="B10">IFERROR(MAX(--_xlfn.TEXTSPLIT(C10,";")),0)</f>
@@ -34522,7 +34648,9 @@
       <c r="D10" s="39" t="s">
         <v>1925</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="39" t="s">
+        <v>1963</v>
+      </c>
       <c r="F10" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34532,23 +34660,29 @@
       <c r="H10" s="79">
         <v>8000000</v>
       </c>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="79"/>
+      <c r="J10" s="81" t="s">
         <v>1926</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="84">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B11" s="85" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B11" s="75" cm="1">
         <f t="array" ref="B11">IFERROR(MAX(--_xlfn.TEXTSPLIT(C11,";")),0)</f>
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1967</v>
       </c>
       <c r="D11" s="39" t="s">
         <v>1927</v>
       </c>
-      <c r="E11" s="39"/>
+      <c r="E11" s="39" t="s">
+        <v>37</v>
+      </c>
       <c r="F11" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34556,28 +34690,33 @@
         <v>1915</v>
       </c>
       <c r="H11" s="79">
-        <v>880000000</v>
-      </c>
-      <c r="I11" s="80" t="s">
+        <v>22600000</v>
+      </c>
+      <c r="I11" s="79" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J11" s="80" t="s">
         <v>1928</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="83">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B12" s="75" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B12" s="85" cm="1">
         <f t="array" ref="B12">IFERROR(MAX(--_xlfn.TEXTSPLIT(C12,";")),0)</f>
-        <v>42</v>
-      </c>
-      <c r="C12">
-        <v>42</v>
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1972</v>
       </c>
       <c r="D12" s="39" t="s">
         <v>1929</v>
       </c>
-      <c r="E12" s="39"/>
+      <c r="E12" s="39" t="s">
+        <v>1964</v>
+      </c>
       <c r="F12" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34585,25 +34724,33 @@
         <v>1915</v>
       </c>
       <c r="H12" s="79">
-        <v>22600000</v>
-      </c>
-      <c r="I12" s="80" t="s">
+        <v>17600000</v>
+      </c>
+      <c r="I12" s="79" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J12" s="80" t="s">
         <v>1930</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="84">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B13" s="85" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B13" s="75" cm="1">
         <f t="array" ref="B13">IFERROR(MAX(--_xlfn.TEXTSPLIT(C13,";")),0)</f>
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1956</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>1931</v>
       </c>
-      <c r="E13" s="39"/>
+      <c r="E13" s="39" t="s">
+        <v>1962</v>
+      </c>
       <c r="F13" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34611,28 +34758,33 @@
         <v>1915</v>
       </c>
       <c r="H13" s="79">
-        <v>17600000</v>
-      </c>
-      <c r="I13" s="80" t="s">
+        <v>155000000</v>
+      </c>
+      <c r="I13" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J13" s="81" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="83">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="84">
         <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B14" s="85" cm="1">
+        <f t="array" ref="B14">IFERROR(MAX(--_xlfn.TEXTSPLIT(C14,";")),0)</f>
         <v>44</v>
       </c>
-      <c r="B14" s="75" cm="1">
-        <f t="array" ref="B14">IFERROR(MAX(--_xlfn.TEXTSPLIT(C14,";")),0)</f>
-        <v>37</v>
-      </c>
       <c r="C14" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D14" s="39" t="s">
         <v>1933</v>
       </c>
-      <c r="E14" s="39"/>
+      <c r="E14" s="39" t="s">
+        <v>1011</v>
+      </c>
       <c r="F14" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34640,80 +34792,101 @@
         <v>1915</v>
       </c>
       <c r="H14" s="79">
-        <v>155000000</v>
-      </c>
-      <c r="I14" s="81" t="s">
+        <v>700000</v>
+      </c>
+      <c r="I14" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J14" s="80" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="84">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B15" s="85" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B15" s="75" cm="1">
         <f t="array" ref="B15">IFERROR(MAX(--_xlfn.TEXTSPLIT(C15,";")),0)</f>
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>1935</v>
       </c>
-      <c r="E15" s="39"/>
+      <c r="E15" s="39" t="s">
+        <v>1965</v>
+      </c>
       <c r="F15" s="76" t="s">
         <v>1914</v>
       </c>
       <c r="G15" s="77" t="s">
         <v>1915</v>
       </c>
-      <c r="H15" s="79">
-        <v>700000</v>
-      </c>
-      <c r="I15" s="80" t="s">
+      <c r="H15" s="82" t="s">
         <v>1936</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="83">
+      <c r="I15" s="82" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J15" s="80" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B16" s="75" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B16" s="85" cm="1">
         <f t="array" ref="B16">IFERROR(MAX(--_xlfn.TEXTSPLIT(C16,";")),0)</f>
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1966</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>1937</v>
-      </c>
-      <c r="E16" s="39"/>
+        <v>1938</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>1962</v>
+      </c>
       <c r="F16" s="76" t="s">
         <v>1914</v>
       </c>
       <c r="G16" s="77" t="s">
         <v>1915</v>
       </c>
-      <c r="H16" s="82" t="s">
-        <v>1938</v>
-      </c>
-      <c r="I16" s="80" t="s">
+      <c r="H16" s="79">
+        <v>276000000</v>
+      </c>
+      <c r="I16" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J16" s="80" t="s">
         <v>1939</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="84">
+    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B17" s="85" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B17" s="75" cm="1">
         <f t="array" ref="B17">IFERROR(MAX(--_xlfn.TEXTSPLIT(C17,";")),0)</f>
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1966</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>1940</v>
       </c>
-      <c r="E17" s="39"/>
+      <c r="E17" s="39" t="s">
+        <v>1962</v>
+      </c>
       <c r="F17" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34721,25 +34894,33 @@
         <v>1915</v>
       </c>
       <c r="H17" s="79">
-        <v>276000000</v>
-      </c>
-      <c r="I17" s="80" t="s">
+        <v>12000000</v>
+      </c>
+      <c r="I17" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J17" s="80" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="83">
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B18" s="75" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B18" s="85" cm="1">
         <f t="array" ref="B18">IFERROR(MAX(--_xlfn.TEXTSPLIT(C18,";")),0)</f>
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="C18" s="88" t="s">
+        <v>1969</v>
       </c>
       <c r="D18" s="39" t="s">
         <v>1942</v>
       </c>
-      <c r="E18" s="39"/>
+      <c r="E18" s="39" t="s">
+        <v>37</v>
+      </c>
       <c r="F18" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34747,16 +34928,19 @@
         <v>1915</v>
       </c>
       <c r="H18" s="79">
-        <v>12000000</v>
-      </c>
-      <c r="I18" s="80" t="s">
+        <v>35000000</v>
+      </c>
+      <c r="I18" s="79" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J18" s="80" t="s">
         <v>1943</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="84">
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B19" s="85" cm="1">
         <f t="array" ref="B19">IFERROR(MAX(--_xlfn.TEXTSPLIT(C19,";")),0)</f>
@@ -34765,7 +34949,9 @@
       <c r="D19" s="39" t="s">
         <v>1944</v>
       </c>
-      <c r="E19" s="39"/>
+      <c r="E19" s="39" t="s">
+        <v>1963</v>
+      </c>
       <c r="F19" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34773,25 +34959,31 @@
         <v>1915</v>
       </c>
       <c r="H19" s="79">
-        <v>35000000</v>
-      </c>
-      <c r="I19" s="80" t="s">
+        <v>32000000</v>
+      </c>
+      <c r="I19" s="79"/>
+      <c r="J19" s="80" t="s">
         <v>1945</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="83">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="84">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B20" s="85" cm="1">
         <f t="array" ref="B20">IFERROR(MAX(--_xlfn.TEXTSPLIT(C20,";")),0)</f>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1957</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>1946</v>
       </c>
-      <c r="E20" s="39"/>
+      <c r="E20" s="39" t="s">
+        <v>1011</v>
+      </c>
       <c r="F20" s="76" t="s">
         <v>1914</v>
       </c>
@@ -34799,68 +34991,47 @@
         <v>1915</v>
       </c>
       <c r="H20" s="79">
-        <v>32000000</v>
-      </c>
-      <c r="I20" s="80" t="s">
+        <v>212000000</v>
+      </c>
+      <c r="I20" s="79" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J20" s="80" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="84">
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="83">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B21" s="85" cm="1">
+        <v>60</v>
+      </c>
+      <c r="B21" s="75" cm="1">
         <f t="array" ref="B21">IFERROR(MAX(--_xlfn.TEXTSPLIT(C21,";")),0)</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>1948</v>
       </c>
-      <c r="E21" s="39"/>
+      <c r="E21" s="39" t="s">
+        <v>1962</v>
+      </c>
       <c r="F21" s="76" t="s">
         <v>1914</v>
       </c>
       <c r="G21" s="77" t="s">
         <v>1915</v>
       </c>
-      <c r="H21" s="79">
-        <v>212000000</v>
-      </c>
-      <c r="I21" s="80" t="s">
+      <c r="H21" s="82" t="s">
         <v>1949</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="83">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B22" s="75" cm="1">
-        <f t="array" ref="B22">IFERROR(MAX(--_xlfn.TEXTSPLIT(C22,";")),0)</f>
-        <v>38</v>
-      </c>
-      <c r="C22">
-        <v>38</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="I21" s="82" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J21" s="80" t="s">
         <v>1950</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="76" t="s">
-        <v>1914</v>
-      </c>
-      <c r="G22" s="77" t="s">
-        <v>1915</v>
-      </c>
-      <c r="H22" s="82" t="s">
-        <v>1951</v>
-      </c>
-      <c r="I22" s="80" t="s">
-        <v>1952</v>
       </c>
     </row>
   </sheetData>

--- a/CATLEC.xlsx
+++ b/CATLEC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edison\Desktop\CATLEC\Codigo CATLEC - backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70DE4E5-7DE6-4238-A58F-309C0DF517BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B88850-3DE4-4DCA-B39B-26B8B41F453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="TD BD" sheetId="3" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4766" uniqueCount="1983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4779" uniqueCount="1992">
   <si>
     <t>Código proyecto</t>
   </si>
@@ -6298,6 +6298,33 @@
   </si>
   <si>
     <t>Filial</t>
+  </si>
+  <si>
+    <t>El proyecto contemplaba la construcción y operación de un puente sobre el canal Chacao que conectara la isla de Chiloé con Chile continental. El contrato se extinguió anticipadamente en 2007 tras dos años de vigencia, no llegando a materializarse la obra. En la actualidad se encuentra en construcción el nuevo proyecto del Puente Chacao, a cargo de la Dirección de Vialidad del Ministerio de Obras Públicas.</t>
+  </si>
+  <si>
+    <t>El proyecto considera la construcción y operación de una Planta Desaladora de agua de mar ubicada en el sector del Panul, junto con sus respectivas obras de conducción de agua para la Región de Coquimbo, la cual tiene por objetivo el abastecimiento de agua potable para el consumo humano de las comunas de Coquimbo y La Serena, con potencial expansión hacia otros sistemas. La iniciativa plantea un servicio de desalinización de agua de mar mediante el sistema de osmósis inversa, con una capacidad de producción estimada de 1.200 litros/segundo, incluyendo además las obras del sistema de captación para la alimentación de la planta, emisario de descarga de salmuera, sistemas de prefiltración así como las obras para el sistema de conducción y bombeo a un estanque de distribución de agua potable de 8.000 m3, preliminarmente ubicado a cerca de 21 km de la planta. La obra beneficiará a una población estimada de 460.000 habitantes de las comunas de Coquimbo y La Serena.</t>
+  </si>
+  <si>
+    <t>SACYR AGUA S.L.</t>
+  </si>
+  <si>
+    <t>El proyecto corresponde al desarrollo de una vía alternativa a la actual Ruta 160, en el tramo entre las comunas de San Pedro de la Paz y Coronel, el que ha experimentado un gran crecimiento en los últimos años. La obra considera un trazado por el borde de los cerros, al oriente de la Ruta 160, que conectará por el norte con la Concesión Vial Puente Industrial, que se encuentra en etapa de construcción, y por el sur con la Concesión Ruta 160, Tramo Coronel – Tres Pinos. Entre los beneficios de la iniciativa destaca el mejoramiento de la conectividad en la Región del Biobío, gracias a la construcción de una ruta de alto estándar, con sistema de pórticos de telepeaje y una velocidad de desplazamiento prevista en 120 km/hora.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SACYR CONCESIONES SPA </t>
+  </si>
+  <si>
+    <t>La obra corresponde al mejoramiento de la Ruta 5 en la provincia de Chiloé en una extensión de 126 km y con un trazado que cruza por las comunas de Ancud, Dalcahue, Castro y Chonchi. El proyecto comienza en el acceso sur del futuro puente sobre el Canal de Chacao y concluye en la bifurcación del acceso norte a Chonchi, considerando además la operación y mantención de aproximadamente 16 kilómetros de camino con perfil de una calzada bidireccional, correspondientes al Bypass Castro. Entre los beneficios de la obra se encuentra disminuir los tiempos de viaje y aumentar la seguridad en el trazado, con ello se prevé que se favorecerá el intercambio comercial, productivo y de servicios en la zona.</t>
+  </si>
+  <si>
+    <t>GRUPO COSTANERA SPA</t>
+  </si>
+  <si>
+    <t>El proyecto corresponde al mejoramiento de la Ruta 5 entre las comunas de Río Bueno y Puerto Montt, con una longitud de 129,8 km aproximadamente. Se proyectan nuevas obras como terceras pistas en algunos sectores, nuevos enlaces y mejoramientos de los existentes, nuevos retornos y atraviesos, reemplazo de puentes existentes que alcanzaron su vida útil, rectificaciones geométricas del trazado, nuevas calles de servicio y ciclovías, reemplazo y nuevas pasarelas con sus respectivos paraderos y circuitos peatonales, iluminación, obras de seguridad vial con el remplazo de todas las barreras de contención para cumplir con las exigencias de la actual normativa, entre otras. La iniciativa considera también la rehabilitación de los pavimentos existentes y el reemplazo de los peajes manuales, para dar paso a un sistema de cobro del tipo telepeaje.</t>
+  </si>
+  <si>
+    <t>INTERVIAL CHILE S.A.</t>
   </si>
 </sst>
 </file>
@@ -6426,7 +6453,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6478,6 +6505,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6597,7 +6630,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6809,6 +6842,7 @@
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -6823,9 +6857,6 @@
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="51">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6843,6 +6874,9 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -12342,7 +12376,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" headerRowCellStyle="Normal_Hoja1">
-  <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}"/>
+  <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}">
+    <filterColumn colId="31">
+      <filters blank="1">
+        <filter val="Conceoción: 10-12-2010: Antofagatsa: 06-03-2012"/>
+        <filter val="En fase de construcción"/>
+        <filter val="No aplica"/>
+        <filter val="Santiago 20-01-2007; Valdivia 22-04-2007;Puerto Montt 27-05-2007"/>
+        <filter val="SD"/>
+        <filter val="Sin inicio de fase de construcción"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AJ128">
     <sortCondition sortBy="cellColor" ref="C1:C128" dxfId="45"/>
   </sortState>
@@ -12421,8 +12466,8 @@
     <tableColumn id="5" xr3:uid="{AFB4B37C-C7FF-4D77-AB2A-762A7D41A8ED}" name="Institucion mandante" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{D863FC92-BAB3-47C2-BB80-F22D29F3D864}" name="Fuente  de inf" dataDxfId="3" dataCellStyle="Hipervínculo"/>
     <tableColumn id="7" xr3:uid="{D3486ADD-FCAB-467D-B0EB-251EEB3E245B}" name="Inversion (USD) " dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{B4EFD4AE-28EB-449A-AD8D-58C9B7719A54}" name="Filial" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{B4EFD4AE-28EB-449A-AD8D-58C9B7719A54}" name="Filial" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13137,7 +13182,7 @@
   <dimension ref="A1:AK128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" customWidth="1"/>
     <col min="6" max="6" width="24.5546875" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
@@ -13162,7 +13207,7 @@
     <col min="27" max="27" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="23" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="35.5546875" customWidth="1"/>
-    <col min="30" max="30" width="29" customWidth="1"/>
+    <col min="30" max="30" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="19.88671875" customWidth="1"/>
     <col min="32" max="32" width="20.6640625" customWidth="1"/>
     <col min="33" max="33" width="30.44140625" customWidth="1"/>
@@ -13285,16 +13330,18 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <f t="shared" ref="B2:B33" si="0">MAX($C$2:$C$128)</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C2" cm="1">
         <f t="array" ref="C2">IFERROR(MAX(--_xlfn.TEXTSPLIT(D2,";")),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="57"/>
+        <v>190</v>
+      </c>
+      <c r="D2" s="91">
+        <v>190</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>381</v>
       </c>
@@ -13399,13 +13446,13 @@
     <row r="3" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C3" cm="1">
         <f t="array" ref="C3">IFERROR(MAX(--_xlfn.TEXTSPLIT(D3,";")),0)</f>
         <v>188</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="1">
         <v>188</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -13420,8 +13467,8 @@
       <c r="H3" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="I3" s="1">
-        <v>0</v>
+      <c r="I3" s="1" t="s">
+        <v>1983</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>36</v>
@@ -13512,7 +13559,7 @@
     <row r="4" spans="1:37" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C4" cm="1">
         <f t="array" ref="C4">IFERROR(MAX(--_xlfn.TEXTSPLIT(D4,";")),0)</f>
@@ -13533,7 +13580,9 @@
       <c r="H4" s="74" t="s">
         <v>1749</v>
       </c>
-      <c r="I4" s="59"/>
+      <c r="I4" s="1" t="s">
+        <v>1984</v>
+      </c>
       <c r="J4" s="59" t="s">
         <v>263</v>
       </c>
@@ -13557,17 +13606,25 @@
       <c r="V4" s="60">
         <v>45944</v>
       </c>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="60">
+        <v>46112</v>
+      </c>
       <c r="Y4" s="60"/>
       <c r="Z4" s="59"/>
-      <c r="AA4" s="59"/>
+      <c r="AA4" s="3" t="s">
+        <v>1985</v>
+      </c>
       <c r="AB4" s="59"/>
-      <c r="AC4" s="60"/>
+      <c r="AC4" s="60">
+        <v>46123</v>
+      </c>
       <c r="AD4" s="60"/>
       <c r="AE4" s="59"/>
       <c r="AF4" s="59"/>
-      <c r="AG4" s="59"/>
+      <c r="AG4" s="2" t="s">
+        <v>697</v>
+      </c>
       <c r="AH4" s="59"/>
       <c r="AI4" s="22"/>
       <c r="AJ4" s="23"/>
@@ -13576,13 +13633,13 @@
         <v>PDRC1</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1890</v>
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" cm="1">
         <f t="array" ref="C5">IFERROR(MAX(--_xlfn.TEXTSPLIT(D5,";")),0)</f>
@@ -13692,13 +13749,13 @@
         <v>160R1</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1891</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C6" cm="1">
         <f t="array" ref="C6">IFERROR(MAX(--_xlfn.TEXTSPLIT(D6,";")),0)</f>
@@ -13811,7 +13868,7 @@
     <row r="7" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C7" cm="1">
         <f t="array" ref="C7">IFERROR(MAX(--_xlfn.TEXTSPLIT(D7,";")),0)</f>
@@ -13924,7 +13981,7 @@
     <row r="8" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" cm="1">
         <f t="array" ref="C8">IFERROR(MAX(--_xlfn.TEXTSPLIT(D8,";")),0)</f>
@@ -14034,13 +14091,13 @@
         <v>2AVO1</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1892</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C9" cm="1">
         <f t="array" ref="C9">IFERROR(MAX(--_xlfn.TEXTSPLIT(D9,";")),0)</f>
@@ -14156,7 +14213,7 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C10" cm="1">
         <f t="array" ref="C10">IFERROR(MAX(--_xlfn.TEXTSPLIT(D10,";")),0)</f>
@@ -14266,13 +14323,13 @@
         <v>60GR1</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1894</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C11" cm="1">
         <f t="array" ref="C11">IFERROR(MAX(--_xlfn.TEXTSPLIT(D11,";")),0)</f>
@@ -14385,7 +14442,7 @@
     <row r="12" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C12" cm="1">
         <f t="array" ref="C12">IFERROR(MAX(--_xlfn.TEXTSPLIT(D12,";")),0)</f>
@@ -14501,7 +14558,7 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" cm="1">
         <f t="array" ref="C13">IFERROR(MAX(--_xlfn.TEXTSPLIT(D13,";")),0)</f>
@@ -14614,7 +14671,7 @@
     <row r="14" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C14" cm="1">
         <f t="array" ref="C14">IFERROR(MAX(--_xlfn.TEXTSPLIT(D14,";")),0)</f>
@@ -14724,13 +14781,13 @@
         <v>67CV1</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1896</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" cm="1">
         <f t="array" ref="C15">IFERROR(MAX(--_xlfn.TEXTSPLIT(D15,";")),0)</f>
@@ -14840,13 +14897,13 @@
         <v>ACIQ1</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1897</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" cm="1">
         <f t="array" ref="C16">IFERROR(MAX(--_xlfn.TEXTSPLIT(D16,";")),0)</f>
@@ -14956,13 +15013,13 @@
         <v>ACNO1</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1898</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" cm="1">
         <f t="array" ref="C17">IFERROR(MAX(--_xlfn.TEXTSPLIT(D17,";")),0)</f>
@@ -15075,7 +15132,7 @@
     <row r="18" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" cm="1">
         <f t="array" ref="C18">IFERROR(MAX(--_xlfn.TEXTSPLIT(D18,";")),0)</f>
@@ -15185,10 +15242,10 @@
         <v>AAMB1</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" cm="1">
         <f t="array" ref="C19">IFERROR(MAX(--_xlfn.TEXTSPLIT(D19,";")),0)</f>
@@ -15298,13 +15355,13 @@
         <v>AAMB2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" ht="244.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1900</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" cm="1">
         <f t="array" ref="C20">IFERROR(MAX(--_xlfn.TEXTSPLIT(D20,";")),0)</f>
@@ -15420,7 +15477,7 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C21" cm="1">
         <f t="array" ref="C21">IFERROR(MAX(--_xlfn.TEXTSPLIT(D21,";")),0)</f>
@@ -15530,10 +15587,10 @@
         <v>ACHA2</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" cm="1">
         <f t="array" ref="C22">IFERROR(MAX(--_xlfn.TEXTSPLIT(D22,";")),0)</f>
@@ -15643,10 +15700,10 @@
         <v>ACIP1</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C23" cm="1">
         <f t="array" ref="C23">IFERROR(MAX(--_xlfn.TEXTSPLIT(D23,";")),0)</f>
@@ -15759,7 +15816,7 @@
     <row r="24" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" cm="1">
         <f t="array" ref="C24">IFERROR(MAX(--_xlfn.TEXTSPLIT(D24,";")),0)</f>
@@ -15869,10 +15926,10 @@
         <v>ANCO2</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C25" cm="1">
         <f t="array" ref="C25">IFERROR(MAX(--_xlfn.TEXTSPLIT(D25,";")),0)</f>
@@ -15982,10 +16039,10 @@
         <v>ACMA1</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C26" cm="1">
         <f t="array" ref="C26">IFERROR(MAX(--_xlfn.TEXTSPLIT(D26,";")),0)</f>
@@ -16095,10 +16152,10 @@
         <v>ACMA2</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C27" cm="1">
         <f t="array" ref="C27">IFERROR(MAX(--_xlfn.TEXTSPLIT(D27,";")),0)</f>
@@ -16208,13 +16265,13 @@
         <v>AURA1</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1901</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" cm="1">
         <f t="array" ref="C28">IFERROR(MAX(--_xlfn.TEXTSPLIT(D28,";")),0)</f>
@@ -16324,13 +16381,13 @@
         <v>ACSU1</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1902</v>
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C29" cm="1">
         <f t="array" ref="C29">IFERROR(MAX(--_xlfn.TEXTSPLIT(D29,";")),0)</f>
@@ -16440,10 +16497,10 @@
         <v>ACSU2</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C30" cm="1">
         <f t="array" ref="C30">IFERROR(MAX(--_xlfn.TEXTSPLIT(D30,";")),0)</f>
@@ -16553,13 +16610,13 @@
         <v>ADAI1</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1904</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C31" cm="1">
         <f t="array" ref="C31">IFERROR(MAX(--_xlfn.TEXTSPLIT(D31,";")),0)</f>
@@ -16669,10 +16726,10 @@
         <v>ADAI2</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" cm="1">
         <f t="array" ref="C32">IFERROR(MAX(--_xlfn.TEXTSPLIT(D32,";")),0)</f>
@@ -16782,13 +16839,13 @@
         <v>ADAI3</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1903</v>
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C33" cm="1">
         <f t="array" ref="C33">IFERROR(MAX(--_xlfn.TEXTSPLIT(D33,";")),0)</f>
@@ -16898,10 +16955,10 @@
         <v>ADAI4</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="147.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" ht="147.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <f t="shared" ref="B34:B65" si="2">MAX($C$2:$C$128)</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C34" cm="1">
         <f t="array" ref="C34">IFERROR(MAX(--_xlfn.TEXTSPLIT(D34,";")),0)</f>
@@ -17011,10 +17068,10 @@
         <v>ALFS1</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C35" cm="1">
         <f t="array" ref="C35">IFERROR(MAX(--_xlfn.TEXTSPLIT(D35,";")),0)</f>
@@ -17127,7 +17184,7 @@
     <row r="36" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C36" cm="1">
         <f t="array" ref="C36">IFERROR(MAX(--_xlfn.TEXTSPLIT(D36,";")),0)</f>
@@ -17237,13 +17294,13 @@
         <v>ALFS3</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1905</v>
       </c>
       <c r="B37" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C37" cm="1">
         <f t="array" ref="C37">IFERROR(MAX(--_xlfn.TEXTSPLIT(D37,";")),0)</f>
@@ -17353,13 +17410,13 @@
         <v>ALOA1</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1906</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C38" cm="1">
         <f t="array" ref="C38">IFERROR(MAX(--_xlfn.TEXTSPLIT(D38,";")),0)</f>
@@ -17472,7 +17529,7 @@
     <row r="39" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" cm="1">
         <f t="array" ref="C39">IFERROR(MAX(--_xlfn.TEXTSPLIT(D39,";")),0)</f>
@@ -17585,7 +17642,7 @@
     <row r="40" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C40" cm="1">
         <f t="array" ref="C40">IFERROR(MAX(--_xlfn.TEXTSPLIT(D40,";")),0)</f>
@@ -17695,10 +17752,10 @@
         <v>AVAM1</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="180" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" ht="180" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C41" cm="1">
         <f t="array" ref="C41">IFERROR(MAX(--_xlfn.TEXTSPLIT(D41,";")),0)</f>
@@ -17808,10 +17865,10 @@
         <v>AVAM2</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C42" cm="1">
         <f t="array" ref="C42">IFERROR(MAX(--_xlfn.TEXTSPLIT(D42,";")),0)</f>
@@ -17924,7 +17981,7 @@
     <row r="43" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C43" cm="1">
         <f t="array" ref="C43">IFERROR(MAX(--_xlfn.TEXTSPLIT(D43,";")),0)</f>
@@ -18035,7 +18092,7 @@
     <row r="44" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C44" cm="1">
         <f t="array" ref="C44">IFERROR(MAX(--_xlfn.TEXTSPLIT(D44,";")),0)</f>
@@ -18145,10 +18202,10 @@
         <v>ATEP1</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C45" cm="1">
         <f t="array" ref="C45">IFERROR(MAX(--_xlfn.TEXTSPLIT(D45,";")),0)</f>
@@ -18258,10 +18315,10 @@
         <v>ATEP2</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" ht="168.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C46" cm="1">
         <f t="array" ref="C46">IFERROR(MAX(--_xlfn.TEXTSPLIT(D46,";")),0)</f>
@@ -18371,10 +18428,10 @@
         <v>ATEP3</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C47" cm="1">
         <f t="array" ref="C47">IFERROR(MAX(--_xlfn.TEXTSPLIT(D47,";")),0)</f>
@@ -18487,7 +18544,7 @@
     <row r="48" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C48" cm="1">
         <f t="array" ref="C48">IFERROR(MAX(--_xlfn.TEXTSPLIT(D48,";")),0)</f>
@@ -18597,10 +18654,10 @@
         <v>AVAM3</v>
       </c>
     </row>
-    <row r="49" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C49" cm="1">
         <f t="array" ref="C49">IFERROR(MAX(--_xlfn.TEXTSPLIT(D49,";")),0)</f>
@@ -18710,10 +18767,10 @@
         <v>AVES1</v>
       </c>
     </row>
-    <row r="50" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C50" cm="1">
         <f t="array" ref="C50">IFERROR(MAX(--_xlfn.TEXTSPLIT(D50,";")),0)</f>
@@ -18823,10 +18880,10 @@
         <v>AVNP1</v>
       </c>
     </row>
-    <row r="51" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C51" cm="1">
         <f t="array" ref="C51">IFERROR(MAX(--_xlfn.TEXTSPLIT(D51,";")),0)</f>
@@ -18936,10 +18993,10 @@
         <v>CDMA1</v>
       </c>
     </row>
-    <row r="52" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C52" cm="1">
         <f t="array" ref="C52">IFERROR(MAX(--_xlfn.TEXTSPLIT(D52,";")),0)</f>
@@ -19052,7 +19109,7 @@
     <row r="53" spans="2:37" ht="242.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C53" cm="1">
         <f t="array" ref="C53">IFERROR(MAX(--_xlfn.TEXTSPLIT(D53,";")),0)</f>
@@ -19162,10 +19219,10 @@
         <v>CHCO2</v>
       </c>
     </row>
-    <row r="54" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C54" cm="1">
         <f t="array" ref="C54">IFERROR(MAX(--_xlfn.TEXTSPLIT(D54,";")),0)</f>
@@ -19275,10 +19332,10 @@
         <v>CNPU1</v>
       </c>
     </row>
-    <row r="55" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C55" cm="1">
         <f t="array" ref="C55">IFERROR(MAX(--_xlfn.TEXTSPLIT(D55,";")),0)</f>
@@ -19391,7 +19448,7 @@
     <row r="56" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C56" cm="1">
         <f t="array" ref="C56">IFERROR(MAX(--_xlfn.TEXTSPLIT(D56,";")),0)</f>
@@ -19501,10 +19558,10 @@
         <v>CNPU2</v>
       </c>
     </row>
-    <row r="57" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C57" cm="1">
         <f t="array" ref="C57">IFERROR(MAX(--_xlfn.TEXTSPLIT(D57,";")),0)</f>
@@ -19614,10 +19671,10 @@
         <v>COCA1</v>
       </c>
     </row>
-    <row r="58" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C58" cm="1">
         <f t="array" ref="C58">IFERROR(MAX(--_xlfn.TEXTSPLIT(D58,";")),0)</f>
@@ -19727,10 +19784,10 @@
         <v>CMVR1</v>
       </c>
     </row>
-    <row r="59" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C59" cm="1">
         <f t="array" ref="C59">IFERROR(MAX(--_xlfn.TEXTSPLIT(D59,";")),0)</f>
@@ -19840,10 +19897,10 @@
         <v>COTE1</v>
       </c>
     </row>
-    <row r="60" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C60" cm="1">
         <f t="array" ref="C60">IFERROR(MAX(--_xlfn.TEXTSPLIT(D60,";")),0)</f>
@@ -19956,7 +20013,7 @@
     <row r="61" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C61" cm="1">
         <f t="array" ref="C61">IFERROR(MAX(--_xlfn.TEXTSPLIT(D61,";")),0)</f>
@@ -20064,10 +20121,10 @@
         <v>ISVV2</v>
       </c>
     </row>
-    <row r="62" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C62" cm="1">
         <f t="array" ref="C62">IFERROR(MAX(--_xlfn.TEXTSPLIT(D62,";")),0)</f>
@@ -20177,10 +20234,10 @@
         <v>LVLS1</v>
       </c>
     </row>
-    <row r="63" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C63" cm="1">
         <f t="array" ref="C63">IFERROR(MAX(--_xlfn.TEXTSPLIT(D63,";")),0)</f>
@@ -20290,10 +20347,10 @@
         <v>CSJS1</v>
       </c>
     </row>
-    <row r="64" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C64" cm="1">
         <f t="array" ref="C64">IFERROR(MAX(--_xlfn.TEXTSPLIT(D64,";")),0)</f>
@@ -20403,10 +20460,10 @@
         <v>CTSR1</v>
       </c>
     </row>
-    <row r="65" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
         <f t="shared" si="2"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C65" cm="1">
         <f t="array" ref="C65">IFERROR(MAX(--_xlfn.TEXTSPLIT(D65,";")),0)</f>
@@ -20516,10 +20573,10 @@
         <v>CVSR1</v>
       </c>
     </row>
-    <row r="66" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1">
         <f t="shared" ref="B66:B97" si="4">MAX($C$2:$C$128)</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C66" cm="1">
         <f t="array" ref="C66">IFERROR(MAX(--_xlfn.TEXTSPLIT(D66,";")),0)</f>
@@ -20632,7 +20689,7 @@
     <row r="67" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C67" cm="1">
         <f t="array" ref="C67">IFERROR(MAX(--_xlfn.TEXTSPLIT(D67,";")),0)</f>
@@ -20742,10 +20799,10 @@
         <v>EEBA1</v>
       </c>
     </row>
-    <row r="68" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C68" cm="1">
         <f t="array" ref="C68">IFERROR(MAX(--_xlfn.TEXTSPLIT(D68,";")),0)</f>
@@ -20858,7 +20915,7 @@
     <row r="69" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C69" cm="1">
         <f t="array" ref="C69">IFERROR(MAX(--_xlfn.TEXTSPLIT(D69,";")),0)</f>
@@ -20971,7 +21028,7 @@
     <row r="70" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C70" cm="1">
         <f t="array" ref="C70">IFERROR(MAX(--_xlfn.TEXTSPLIT(D70,";")),0)</f>
@@ -21082,7 +21139,7 @@
     <row r="71" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C71" cm="1">
         <f t="array" ref="C71">IFERROR(MAX(--_xlfn.TEXTSPLIT(D71,";")),0)</f>
@@ -21192,10 +21249,10 @@
         <v>EPUN1</v>
       </c>
     </row>
-    <row r="72" spans="2:37" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:37" ht="150" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C72" cm="1">
         <f t="array" ref="C72">IFERROR(MAX(--_xlfn.TEXTSPLIT(D72,";")),0)</f>
@@ -21305,10 +21362,10 @@
         <v>ETPO1</v>
       </c>
     </row>
-    <row r="73" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C73" cm="1">
         <f t="array" ref="C73">IFERROR(MAX(--_xlfn.TEXTSPLIT(D73,";")),0)</f>
@@ -21421,7 +21478,7 @@
     <row r="74" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C74" cm="1">
         <f t="array" ref="C74">IFERROR(MAX(--_xlfn.TEXTSPLIT(D74,";")),0)</f>
@@ -21534,7 +21591,7 @@
     <row r="75" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C75" cm="1">
         <f t="array" ref="C75">IFERROR(MAX(--_xlfn.TEXTSPLIT(D75,";")),0)</f>
@@ -21647,7 +21704,7 @@
     <row r="76" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C76" cm="1">
         <f t="array" ref="C76">IFERROR(MAX(--_xlfn.TEXTSPLIT(D76,";")),0)</f>
@@ -21760,7 +21817,7 @@
     <row r="77" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C77" cm="1">
         <f t="array" ref="C77">IFERROR(MAX(--_xlfn.TEXTSPLIT(D77,";")),0)</f>
@@ -21873,7 +21930,7 @@
     <row r="78" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C78" cm="1">
         <f t="array" ref="C78">IFERROR(MAX(--_xlfn.TEXTSPLIT(D78,";")),0)</f>
@@ -21984,7 +22041,7 @@
     <row r="79" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C79" cm="1">
         <f t="array" ref="C79">IFERROR(MAX(--_xlfn.TEXTSPLIT(D79,";")),0)</f>
@@ -22097,7 +22154,7 @@
     <row r="80" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C80" cm="1">
         <f t="array" ref="C80">IFERROR(MAX(--_xlfn.TEXTSPLIT(D80,";")),0)</f>
@@ -22210,7 +22267,7 @@
     <row r="81" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C81" cm="1">
         <f t="array" ref="C81">IFERROR(MAX(--_xlfn.TEXTSPLIT(D81,";")),0)</f>
@@ -22320,10 +22377,10 @@
         <v>HRRL1</v>
       </c>
     </row>
-    <row r="82" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C82" cm="1">
         <f t="array" ref="C82">IFERROR(MAX(--_xlfn.TEXTSPLIT(D82,";")),0)</f>
@@ -22433,10 +22490,10 @@
         <v>HSAN1</v>
       </c>
     </row>
-    <row r="83" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C83" cm="1">
         <f t="array" ref="C83">IFERROR(MAX(--_xlfn.TEXTSPLIT(D83,";")),0)</f>
@@ -22546,10 +22603,10 @@
         <v>HSFB1</v>
       </c>
     </row>
-    <row r="84" spans="1:37" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:37" ht="223.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">IFERROR(MAX(--_xlfn.TEXTSPLIT(D84,";")),0)</f>
@@ -22662,7 +22719,7 @@
     <row r="85" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" cm="1">
         <f t="array" ref="C85">IFERROR(MAX(--_xlfn.TEXTSPLIT(D85,";")),0)</f>
@@ -22775,7 +22832,7 @@
     <row r="86" spans="1:37" ht="148.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">IFERROR(MAX(--_xlfn.TEXTSPLIT(D86,";")),0)</f>
@@ -22888,7 +22945,7 @@
     <row r="87" spans="1:37" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C87" cm="1">
         <f t="array" ref="C87">IFERROR(MAX(--_xlfn.TEXTSPLIT(D87,";")),0)</f>
@@ -22998,13 +23055,13 @@
         <v>LVLS2</v>
       </c>
     </row>
-    <row r="88" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1907</v>
       </c>
       <c r="B88" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">IFERROR(MAX(--_xlfn.TEXTSPLIT(D88,";")),0)</f>
@@ -23117,7 +23174,7 @@
     <row r="89" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">IFERROR(MAX(--_xlfn.TEXTSPLIT(D89,";")),0)</f>
@@ -23227,10 +23284,10 @@
         <v>ORSS1</v>
       </c>
     </row>
-    <row r="90" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C90" cm="1">
         <f t="array" ref="C90">IFERROR(MAX(--_xlfn.TEXTSPLIT(D90,";")),0)</f>
@@ -23343,7 +23400,7 @@
     <row r="91" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C91" cm="1">
         <f t="array" ref="C91">IFERROR(MAX(--_xlfn.TEXTSPLIT(D91,";")),0)</f>
@@ -23451,10 +23508,10 @@
         <v>NARA2</v>
       </c>
     </row>
-    <row r="92" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C92" cm="1">
         <f t="array" ref="C92">IFERROR(MAX(--_xlfn.TEXTSPLIT(D92,";")),0)</f>
@@ -23564,10 +23621,10 @@
         <v>PMPA1</v>
       </c>
     </row>
-    <row r="93" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C93" cm="1">
         <f t="array" ref="C93">IFERROR(MAX(--_xlfn.TEXTSPLIT(D93,";")),0)</f>
@@ -23680,7 +23737,7 @@
     <row r="94" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C94" cm="1">
         <f t="array" ref="C94">IFERROR(MAX(--_xlfn.TEXTSPLIT(D94,";")),0)</f>
@@ -23699,7 +23756,9 @@
       <c r="H94" s="62" t="s">
         <v>1737</v>
       </c>
-      <c r="I94" s="59"/>
+      <c r="I94" s="1" t="s">
+        <v>1990</v>
+      </c>
       <c r="J94" s="59" t="s">
         <v>36</v>
       </c>
@@ -23707,7 +23766,9 @@
         <v>198</v>
       </c>
       <c r="L94" s="59"/>
-      <c r="M94" s="59"/>
+      <c r="M94" s="59" t="s">
+        <v>39</v>
+      </c>
       <c r="N94" s="60"/>
       <c r="O94" s="61"/>
       <c r="P94" s="59"/>
@@ -23717,17 +23778,29 @@
       </c>
       <c r="S94" s="59"/>
       <c r="T94" s="59"/>
-      <c r="U94" s="60"/>
-      <c r="V94" s="60"/>
-      <c r="W94" s="60"/>
+      <c r="U94" s="60">
+        <v>45835</v>
+      </c>
+      <c r="V94" s="60">
+        <v>46085</v>
+      </c>
+      <c r="W94" s="60">
+        <v>46113</v>
+      </c>
       <c r="X94" s="60"/>
       <c r="Y94" s="60"/>
       <c r="Z94" s="59"/>
-      <c r="AA94" s="59"/>
+      <c r="AA94" s="59" t="s">
+        <v>1991</v>
+      </c>
       <c r="AB94" s="59"/>
-      <c r="AC94" s="60"/>
+      <c r="AC94" s="60">
+        <v>46186</v>
+      </c>
       <c r="AD94" s="60"/>
-      <c r="AE94" s="59"/>
+      <c r="AE94" s="59" t="s">
+        <v>106</v>
+      </c>
       <c r="AF94" s="59"/>
       <c r="AG94" s="59"/>
       <c r="AH94" s="59"/>
@@ -23738,10 +23811,10 @@
         <v>RBPM2</v>
       </c>
     </row>
-    <row r="95" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C95" cm="1">
         <f t="array" ref="C95">IFERROR(MAX(--_xlfn.TEXTSPLIT(D95,";")),0)</f>
@@ -23851,10 +23924,10 @@
         <v>PCIS1</v>
       </c>
     </row>
-    <row r="96" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C96" cm="1">
         <f t="array" ref="C96">IFERROR(MAX(--_xlfn.TEXTSPLIT(D96,";")),0)</f>
@@ -23964,10 +24037,10 @@
         <v>RITP1</v>
       </c>
     </row>
-    <row r="97" spans="2:37" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:37" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C97" cm="1">
         <f t="array" ref="C97">IFERROR(MAX(--_xlfn.TEXTSPLIT(D97,";")),0)</f>
@@ -24080,7 +24153,7 @@
     <row r="98" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1">
         <f t="shared" ref="B98:B128" si="6">MAX($C$2:$C$128)</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C98" cm="1">
         <f t="array" ref="C98">IFERROR(MAX(--_xlfn.TEXTSPLIT(D98,";")),0)</f>
@@ -24193,7 +24266,7 @@
     <row r="99" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C99" cm="1">
         <f t="array" ref="C99">IFERROR(MAX(--_xlfn.TEXTSPLIT(D99,";")),0)</f>
@@ -24306,7 +24379,7 @@
     <row r="100" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C100" cm="1">
         <f t="array" ref="C100">IFERROR(MAX(--_xlfn.TEXTSPLIT(D100,";")),0)</f>
@@ -24419,7 +24492,7 @@
     <row r="101" spans="2:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C101" cm="1">
         <f t="array" ref="C101">IFERROR(MAX(--_xlfn.TEXTSPLIT(D101,";")),0)</f>
@@ -24527,10 +24600,10 @@
         <v>PP4T1</v>
       </c>
     </row>
-    <row r="102" spans="2:37" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:37" ht="131.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C102" cm="1">
         <f t="array" ref="C102">IFERROR(MAX(--_xlfn.TEXTSPLIT(D102,";")),0)</f>
@@ -24643,7 +24716,7 @@
     <row r="103" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C103" cm="1">
         <f t="array" ref="C103">IFERROR(MAX(--_xlfn.TEXTSPLIT(D103,";")),0)</f>
@@ -24756,7 +24829,7 @@
     <row r="104" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C104" cm="1">
         <f t="array" ref="C104">IFERROR(MAX(--_xlfn.TEXTSPLIT(D104,";")),0)</f>
@@ -24869,7 +24942,7 @@
     <row r="105" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C105" cm="1">
         <f t="array" ref="C105">IFERROR(MAX(--_xlfn.TEXTSPLIT(D105,";")),0)</f>
@@ -24980,7 +25053,7 @@
     <row r="106" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C106" cm="1">
         <f t="array" ref="C106">IFERROR(MAX(--_xlfn.TEXTSPLIT(D106,";")),0)</f>
@@ -25090,10 +25163,10 @@
         <v>RNAH1</v>
       </c>
     </row>
-    <row r="107" spans="2:37" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:37" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C107" cm="1">
         <f t="array" ref="C107">IFERROR(MAX(--_xlfn.TEXTSPLIT(D107,";")),0)</f>
@@ -25114,7 +25187,9 @@
       <c r="H107" s="58" t="s">
         <v>1735</v>
       </c>
-      <c r="I107" s="59"/>
+      <c r="I107" s="59" t="s">
+        <v>1986</v>
+      </c>
       <c r="J107" s="59" t="s">
         <v>36</v>
       </c>
@@ -25132,15 +25207,25 @@
       </c>
       <c r="S107" s="59"/>
       <c r="T107" s="59"/>
-      <c r="U107" s="60"/>
-      <c r="V107" s="60"/>
-      <c r="W107" s="60"/>
+      <c r="U107" s="60">
+        <v>45281</v>
+      </c>
+      <c r="V107" s="60">
+        <v>45930</v>
+      </c>
+      <c r="W107" s="60">
+        <v>45928</v>
+      </c>
       <c r="X107" s="60"/>
       <c r="Y107" s="60"/>
       <c r="Z107" s="59"/>
-      <c r="AA107" s="59"/>
+      <c r="AA107" s="3" t="s">
+        <v>1987</v>
+      </c>
       <c r="AB107" s="59"/>
-      <c r="AC107" s="60"/>
+      <c r="AC107" s="60">
+        <v>46197</v>
+      </c>
       <c r="AD107" s="60"/>
       <c r="AE107" s="59"/>
       <c r="AF107" s="59"/>
@@ -25156,7 +25241,7 @@
     <row r="108" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C108" cm="1">
         <f t="array" ref="C108">IFERROR(MAX(--_xlfn.TEXTSPLIT(D108,";")),0)</f>
@@ -25172,8 +25257,12 @@
         <v>1736</v>
       </c>
       <c r="G108" s="59"/>
-      <c r="H108" s="58"/>
-      <c r="I108" s="59"/>
+      <c r="H108" t="s">
+        <v>1736</v>
+      </c>
+      <c r="I108" s="74" t="s">
+        <v>1988</v>
+      </c>
       <c r="J108" s="59" t="s">
         <v>36</v>
       </c>
@@ -25191,15 +25280,25 @@
       </c>
       <c r="S108" s="59"/>
       <c r="T108" s="59"/>
-      <c r="U108" s="60"/>
-      <c r="V108" s="60"/>
-      <c r="W108" s="60"/>
+      <c r="U108" s="60">
+        <v>44355</v>
+      </c>
+      <c r="V108" s="60">
+        <v>45812</v>
+      </c>
+      <c r="W108" s="60">
+        <v>45840</v>
+      </c>
       <c r="X108" s="60"/>
       <c r="Y108" s="60"/>
       <c r="Z108" s="59"/>
-      <c r="AA108" s="59"/>
+      <c r="AA108" s="59" t="s">
+        <v>1989</v>
+      </c>
       <c r="AB108" s="59"/>
-      <c r="AC108" s="60"/>
+      <c r="AC108" s="60">
+        <v>46066</v>
+      </c>
       <c r="AD108" s="60"/>
       <c r="AE108" s="59"/>
       <c r="AF108" s="59"/>
@@ -25212,10 +25311,10 @@
         <v>RTCC</v>
       </c>
     </row>
-    <row r="109" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C109" cm="1">
         <f t="array" ref="C109">IFERROR(MAX(--_xlfn.TEXTSPLIT(D109,";")),0)</f>
@@ -25325,10 +25424,10 @@
         <v>RVLC1</v>
       </c>
     </row>
-    <row r="110" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C110" cm="1">
         <f t="array" ref="C110">IFERROR(MAX(--_xlfn.TEXTSPLIT(D110,";")),0)</f>
@@ -25441,7 +25540,7 @@
     <row r="111" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C111" cm="1">
         <f t="array" ref="C111">IFERROR(MAX(--_xlfn.TEXTSPLIT(D111,";")),0)</f>
@@ -25549,10 +25648,10 @@
         <v>SALV2</v>
       </c>
     </row>
-    <row r="112" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C112" cm="1">
         <f t="array" ref="C112">IFERROR(MAX(--_xlfn.TEXTSPLIT(D112,";")),0)</f>
@@ -25665,7 +25764,7 @@
     <row r="113" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C113" cm="1">
         <f t="array" ref="C113">IFERROR(MAX(--_xlfn.TEXTSPLIT(D113,";")),0)</f>
@@ -25775,10 +25874,10 @@
         <v>SASA2</v>
       </c>
     </row>
-    <row r="114" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C114" cm="1">
         <f t="array" ref="C114">IFERROR(MAX(--_xlfn.TEXTSPLIT(D114,";")),0)</f>
@@ -25888,10 +25987,10 @@
         <v>SATA1</v>
       </c>
     </row>
-    <row r="115" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C115" cm="1">
         <f t="array" ref="C115">IFERROR(MAX(--_xlfn.TEXTSPLIT(D115,";")),0)</f>
@@ -26001,10 +26100,10 @@
         <v>SCLA1</v>
       </c>
     </row>
-    <row r="116" spans="1:37" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:37" ht="132.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C116" cm="1">
         <f t="array" ref="C116">IFERROR(MAX(--_xlfn.TEXTSPLIT(D116,";")),0)</f>
@@ -26114,10 +26213,10 @@
         <v>SNSS1</v>
       </c>
     </row>
-    <row r="117" spans="1:37" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:37" ht="155.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C117" cm="1">
         <f t="array" ref="C117">IFERROR(MAX(--_xlfn.TEXTSPLIT(D117,";")),0)</f>
@@ -26227,10 +26326,10 @@
         <v>SOPN1</v>
       </c>
     </row>
-    <row r="118" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C118" cm="1">
         <f t="array" ref="C118">IFERROR(MAX(--_xlfn.TEXTSPLIT(D118,";")),0)</f>
@@ -26343,7 +26442,7 @@
     <row r="119" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C119" cm="1">
         <f t="array" ref="C119">IFERROR(MAX(--_xlfn.TEXTSPLIT(D119,";")),0)</f>
@@ -26456,7 +26555,7 @@
     <row r="120" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C120" cm="1">
         <f t="array" ref="C120">IFERROR(MAX(--_xlfn.TEXTSPLIT(D120,";")),0)</f>
@@ -26566,13 +26665,13 @@
         <v>TELB1</v>
       </c>
     </row>
-    <row r="121" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1889</v>
       </c>
       <c r="B121" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C121" cm="1">
         <f t="array" ref="C121">IFERROR(MAX(--_xlfn.TEXTSPLIT(D121,";")),0)</f>
@@ -26682,10 +26781,10 @@
         <v>TEME1</v>
       </c>
     </row>
-    <row r="122" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C122" cm="1">
         <f t="array" ref="C122">IFERROR(MAX(--_xlfn.TEXTSPLIT(D122,";")),0)</f>
@@ -26795,10 +26894,10 @@
         <v>TEME2</v>
       </c>
     </row>
-    <row r="123" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:37" ht="118.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C123" cm="1">
         <f t="array" ref="C123">IFERROR(MAX(--_xlfn.TEXTSPLIT(D123,";")),0)</f>
@@ -26911,7 +27010,7 @@
     <row r="124" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C124" cm="1">
         <f t="array" ref="C124">IFERROR(MAX(--_xlfn.TEXTSPLIT(D124,";")),0)</f>
@@ -27019,10 +27118,10 @@
         <v>TERB2</v>
       </c>
     </row>
-    <row r="125" spans="1:37" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:37" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C125" cm="1">
         <f t="array" ref="C125">IFERROR(MAX(--_xlfn.TEXTSPLIT(D125,";")),0)</f>
@@ -27132,10 +27231,10 @@
         <v>VALS1</v>
       </c>
     </row>
-    <row r="126" spans="1:37" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:37" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C126" cm="1">
         <f t="array" ref="C126">IFERROR(MAX(--_xlfn.TEXTSPLIT(D126,";")),0)</f>
@@ -27245,10 +27344,10 @@
         <v>VAME1</v>
       </c>
     </row>
-    <row r="127" spans="1:37" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:37" ht="125.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C127" cm="1">
         <f t="array" ref="C127">IFERROR(MAX(--_xlfn.TEXTSPLIT(D127,";")),0)</f>
@@ -27358,10 +27457,10 @@
         <v>VCAL1</v>
       </c>
     </row>
-    <row r="128" spans="1:37" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:37" ht="259.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C128" cm="1">
         <f t="array" ref="C128">IFERROR(MAX(--_xlfn.TEXTSPLIT(D128,";")),0)</f>

--- a/CATLEC.xlsx
+++ b/CATLEC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edison\Desktop\CATLEC\Codigo CATLEC - backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A67E3-C97B-42B7-831F-385EF22EC400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043F4E4-6C89-478E-BFC1-B6A5AC3E129B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
   </bookViews>
@@ -5581,9 +5581,6 @@
     <t>aux</t>
   </si>
   <si>
-    <t>XXX_RTCC</t>
-  </si>
-  <si>
     <t>XXX_RBPM2</t>
   </si>
   <si>
@@ -6328,6 +6325,9 @@
   </si>
   <si>
     <t>https://www.google.com/maps/embed?pb=!4v1786064085044!6m8!1m7!1s4STbpFzicvyp9eKxL-chnA!2m2!1d-27.63178747937239!2d-70.46071631954857!3f186.63886624916177!4f-2.7210265584033095!5f0.7820865974627469</t>
+  </si>
+  <si>
+    <t>XXX_RTCC1</t>
   </si>
 </sst>
 </file>
@@ -6853,15 +6853,7 @@
     <cellStyle name="Normal_Hoja4" xfId="6" xr:uid="{84239E63-E84F-41D3-AB64-BCC2124F9300}"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="50">
     <dxf>
       <font>
         <b val="0"/>
@@ -12349,7 +12341,7 @@
     <dataField name="Cuenta de Código proyecto" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="50">
+    <format dxfId="49">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -12372,51 +12364,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" headerRowCellStyle="Normal_Hoja1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}" name="Tabla1" displayName="Tabla1" ref="B1:AJ128" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" headerRowCellStyle="Normal_Hoja1">
   <autoFilter ref="B1:AJ128" xr:uid="{1D629CF4-C472-4B9E-A105-412493DC473F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:AJ124">
     <sortCondition descending="1" ref="C1:C128"/>
   </sortState>
   <tableColumns count="35">
-    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="45">
+    <tableColumn id="35" xr3:uid="{51A86E7B-74D4-4FC2-AD10-E5089F2EAB7C}" name="Max" dataDxfId="44">
       <calculatedColumnFormula>MAX($C$2:$C$128)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="44">
+    <tableColumn id="33" xr3:uid="{B847CA8D-C350-4F19-B0B8-2917E9EC5B6C}" name="Aux" dataDxfId="43">
       <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(D2,";")),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="43"/>
+    <tableColumn id="36" xr3:uid="{E47F5A70-B048-4DBD-9AF1-48355874D056}" name="Shapes" dataDxfId="42"/>
     <tableColumn id="1" xr3:uid="{EBDE2C74-BB18-41CD-8BA6-80BB4E8B06B1}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="42" dataCellStyle="Normal_Hoja4"/>
-    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{8994AC55-2992-4943-AB61-CF0DD8F7A78E}" name="Nombre de la Concesión " dataDxfId="41" dataCellStyle="Normal_Hoja4"/>
+    <tableColumn id="3" xr3:uid="{199CE7EE-D5DD-4FFA-88F3-4B42D02F42E8}" name="NUM_Lic" dataDxfId="40"/>
     <tableColumn id="4" xr3:uid="{01B27C31-31AA-4F49-A1FD-C3C1240EB455}" name="Nombre de uso común"/>
-    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="25"/>
-    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="23"/>
-    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="22"/>
-    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="21"/>
-    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="20"/>
-    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="19"/>
-    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="18"/>
-    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="17"/>
-    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="16"/>
-    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="15"/>
-    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="14"/>
-    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="13" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{64C5A640-42EC-4144-B04D-666608CEAFE2}" name="Descripción " dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{13C62034-984D-4E5D-AB34-D275E07F5CFF}" name="Sector del proyecto" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{A8E1B4AC-7E7D-43EE-B773-2387BED2697E}" name="Región geográfica" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{ACB4D0A1-A214-4257-9A64-04AE08CBDCF0}" name="Link a mapa página web" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{3F605780-9F24-461D-9698-7F8452C70D1E}" name="Origen" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{281D68A1-621E-4015-9C81-9D94E9998382}" name="Fecha resolución declaración interes público" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{13DDD2FD-8CA4-42D3-A2D5-F76365E0DBED}" name="Presupuesto oficial estimado" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{AFC4B2C5-540B-4756-B680-CD2A7629D579}" name="Moneda" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{4FD5FD1D-7705-4B4C-9A2E-A7A7BAF6E82D}" name="Link pagina web concesiones" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{FF0D18CC-FA0A-42A1-95D9-3698F56C5ACF}" name="ESTADO" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{3AE3E861-AFBE-4630-8BED-5CA5A76395D3}" name="Metodo de licitación" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{D61F26D9-4B85-4C5D-85EF-D8159E5D7FA1}" name="Variable(s) de licitación" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{9687CFD7-71C4-4072-BAAA-7FC78075F6B1}" name="Fecha llamado a licitación" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{F33696E1-7AD1-464F-9199-3F6F741E9835}" name="Fecha recepción ofertas" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{756DB67B-EA63-48D3-8F28-59AF88366085}" name="Fecha apertura económica" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{22F790CF-19CD-4603-BF9F-2587C5A71936}" name="Fecha decreto adjudicación" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{BB8AEA3E-D460-4F64-81D2-E3D08FB6D544}" name="Fecha publicación decreto adjudicación" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{3A2DC6EE-EA8A-40F7-BAE0-1EA6BE4B5481}" name="Rut sociedad Concesionaria" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{83CA2B19-8A13-4C41-9638-871A8314B5E6}" name="Nombre sociedad concesionaria" dataDxfId="21"/>
+    <tableColumn id="24" xr3:uid="{31D5D919-9566-44A9-BDE9-6FEF13E2901A}" name="Link a CMF de SC" dataDxfId="20"/>
+    <tableColumn id="25" xr3:uid="{2862DEB5-FE1F-45DF-BCB8-740E1822719D}" name="Fecha inicio del contrato de concesión" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{B7C7929B-54AB-4155-9E19-ACF37DC76466}" name="Fecha término de la concesión" dataDxfId="18"/>
+    <tableColumn id="27" xr3:uid="{90E5B86B-AE98-44B1-B104-70965591C697}" name="Plazo fijo / variable " dataDxfId="17"/>
+    <tableColumn id="28" xr3:uid="{E800A02A-FACD-4C1E-B7D3-B714F52FD9DD}" name="Fecha inicio de obras" dataDxfId="16"/>
+    <tableColumn id="29" xr3:uid="{D75CEDED-9144-4A02-857E-1E11FE744D55}" name="Fecha puesta servicio provisorio" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{9306ADC6-CB38-41A8-854D-C5D6E10C5C6B}" name="Fecha puesta servicio definitivo" dataDxfId="14"/>
+    <tableColumn id="31" xr3:uid="{7DEE930E-F463-4177-8D0D-8158058CE5A6}" name="Inversión Materializada estimada" dataDxfId="13"/>
+    <tableColumn id="32" xr3:uid="{815A6E54-D54F-4981-A920-452331C73487}" name="% Avance obras físicas" dataDxfId="12" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12427,9 +12419,9 @@
   <autoFilter ref="A1:E398" xr:uid="{0B1BCE94-7066-4FA3-AA56-13A528EB24C5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6692F8DC-A6AC-4EB7-BFE9-9CB212613C31}" name="Código proyecto"/>
-    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{4C6BB9F1-9A8B-475A-9BDA-220BF0E3DFB2}" name="Nombre de uso común" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{09EFDC4D-986E-43B3-BC94-7B7B41772935}" name="Codigo oferente"/>
-    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{6598E2A9-FC2E-4DDA-AF0A-F94F4B12052E}" name="Nombre oferente" dataDxfId="10"/>
     <tableColumn id="5" xr3:uid="{F65361E4-8D72-41BE-9F75-3733E402179A}" name="Adjudicado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12437,23 +12429,23 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}" name="Tabla5" displayName="Tabla5" ref="A1:J21" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}" name="Tabla5" displayName="Tabla5" ref="A1:J21" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:J21" xr:uid="{3E5DCCE2-1A06-45E1-9362-F498B312CF33}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1EA8F6C1-92AF-464C-97F8-5259DBA7CBB5}" name="max" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{1EA8F6C1-92AF-464C-97F8-5259DBA7CBB5}" name="max" dataDxfId="8">
       <calculatedColumnFormula>MAX($B$2:$B$127)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33793EA3-34D7-4D6D-B86D-3F250842C10A}" name="aux" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{33793EA3-34D7-4D6D-B86D-3F250842C10A}" name="aux" dataDxfId="7">
       <calculatedColumnFormula array="1">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{14343C55-2461-432C-9954-29952162B76E}" name="Shapes"/>
-    <tableColumn id="4" xr3:uid="{0A185E16-2B61-4FF8-AF73-88336466F284}" name="Proyecto" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{7C61B78F-F4DD-4F80-8D4D-AABD3B55036C}" name="region" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{AFB4B37C-C7FF-4D77-AB2A-762A7D41A8ED}" name="Institucion mandante" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{D863FC92-BAB3-47C2-BB80-F22D29F3D864}" name="Fuente  de inf" dataDxfId="4" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="7" xr3:uid="{D3486ADD-FCAB-467D-B0EB-251EEB3E245B}" name="Inversion (USD) " dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{B4EFD4AE-28EB-449A-AD8D-58C9B7719A54}" name="Filial" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{0A185E16-2B61-4FF8-AF73-88336466F284}" name="Proyecto" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{7C61B78F-F4DD-4F80-8D4D-AABD3B55036C}" name="region" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{AFB4B37C-C7FF-4D77-AB2A-762A7D41A8ED}" name="Institucion mandante" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{D863FC92-BAB3-47C2-BB80-F22D29F3D864}" name="Fuente  de inf" dataDxfId="3" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{D3486ADD-FCAB-467D-B0EB-251EEB3E245B}" name="Inversion (USD) " dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{B4EFD4AE-28EB-449A-AD8D-58C9B7719A54}" name="Filial" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9234F28E-E88E-4763-A76E-73B745ADAF0C}" name="Descripcion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13206,16 +13198,16 @@
   <sheetData>
     <row r="1" spans="1:37" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="C1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E1" s="28" t="s">
         <v>0</v>
@@ -13319,7 +13311,7 @@
     </row>
     <row r="2" spans="1:37" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
-        <f t="shared" ref="B2:B33" si="0">MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B2" si="0">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C2" cm="1">
@@ -13426,13 +13418,13 @@
         <v>0</v>
       </c>
       <c r="AK2" s="69" t="str">
-        <f t="shared" ref="AK2:AK33" si="1">MID(E2,5,LEN(E2)-4)</f>
+        <f t="shared" ref="AK2" si="1">MID(E2,5,LEN(E2)-4)</f>
         <v>EIMQ1</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B3:B34" si="2">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C3" cm="1">
@@ -13455,7 +13447,7 @@
         <v>367</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>36</v>
@@ -13539,13 +13531,13 @@
         <v>0</v>
       </c>
       <c r="AK3" s="69" t="str">
-        <f>MID(E3,5,LEN(E3)-4)</f>
+        <f t="shared" ref="AK3:AK34" si="3">MID(E3,5,LEN(E3)-4)</f>
         <v>PBCH1</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C4" cm="1">
@@ -13553,10 +13545,10 @@
         <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="F4" s="60" t="s">
         <v>1734</v>
@@ -13565,10 +13557,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="72" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="J4" s="57" t="s">
         <v>263</v>
@@ -13600,7 +13592,7 @@
       <c r="Y4" s="58"/>
       <c r="Z4" s="57"/>
       <c r="AA4" s="3" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AB4" s="57"/>
       <c r="AC4" s="58">
@@ -13616,16 +13608,16 @@
       <c r="AI4" s="22"/>
       <c r="AJ4" s="23"/>
       <c r="AK4" s="69" t="str">
-        <f>MID(E4,5,LEN(E4)-4)</f>
+        <f t="shared" si="3"/>
         <v>PDRC1</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B5" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C5" cm="1">
@@ -13633,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>479</v>
@@ -13732,16 +13724,16 @@
         <v>1</v>
       </c>
       <c r="AK5" s="69" t="str">
-        <f>MID(E5,5,LEN(E5)-4)</f>
+        <f t="shared" si="3"/>
         <v>160R1</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B6" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C6" cm="1">
@@ -13749,13 +13741,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>674</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -13848,13 +13840,13 @@
         <v>1</v>
       </c>
       <c r="AK6" s="69" t="str">
-        <f>MID(E6,5,LEN(E6)-4)</f>
+        <f t="shared" si="3"/>
         <v>1AVO1</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C7" cm="1">
@@ -13862,7 +13854,7 @@
         <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>999</v>
@@ -13959,13 +13951,13 @@
         <v>269</v>
       </c>
       <c r="AK7" s="69" t="str">
-        <f>MID(E7,5,LEN(E7)-4)</f>
+        <f t="shared" si="3"/>
         <v>PP4T1</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C8" cm="1">
@@ -13973,13 +13965,13 @@
         <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -14072,16 +14064,16 @@
         <v>1</v>
       </c>
       <c r="AK8" s="69" t="str">
-        <f>MID(E8,5,LEN(E8)-4)</f>
+        <f t="shared" si="3"/>
         <v>PP3G1</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B9" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C9" cm="1">
@@ -14089,13 +14081,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>615</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -14188,16 +14180,16 @@
         <v>1</v>
       </c>
       <c r="AK9" s="69" t="str">
-        <f>MID(E9,5,LEN(E9)-4)</f>
+        <f t="shared" si="3"/>
         <v>43RU1</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B10" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C10" cm="1">
@@ -14205,7 +14197,7 @@
         <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>349</v>
@@ -14304,16 +14296,16 @@
         <v>0</v>
       </c>
       <c r="AK10" s="69" t="str">
-        <f>MID(E10,5,LEN(E10)-4)</f>
+        <f t="shared" si="3"/>
         <v>PP2G1</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B11" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C11" cm="1">
@@ -14321,7 +14313,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>333</v>
@@ -14420,13 +14412,13 @@
         <v>1</v>
       </c>
       <c r="AK11" s="69" t="str">
-        <f>MID(E11,5,LEN(E11)-4)</f>
+        <f t="shared" si="3"/>
         <v>60RU1</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C12" cm="1">
@@ -14434,7 +14426,7 @@
         <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>569</v>
@@ -14533,16 +14525,16 @@
         <v>1</v>
       </c>
       <c r="AK12" s="69" t="str">
-        <f>MID(E12,5,LEN(E12)-4)</f>
+        <f t="shared" si="3"/>
         <v>PP2G2</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B13" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C13" cm="1">
@@ -14550,19 +14542,19 @@
         <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E13" s="45" t="s">
         <v>1017</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="G13" s="1">
         <v>2</v>
       </c>
       <c r="H13" s="45" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>1019</v>
@@ -14647,13 +14639,13 @@
         <v>0</v>
       </c>
       <c r="AK13" s="69" t="str">
-        <f>MID(E13,5,LEN(E13)-4)</f>
+        <f t="shared" si="3"/>
         <v>TERB2</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C14" cm="1">
@@ -14661,13 +14653,13 @@
         <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>778</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -14760,16 +14752,16 @@
         <v>0.57709999999999995</v>
       </c>
       <c r="AK14" s="69" t="str">
-        <f>MID(E14,5,LEN(E14)-4)</f>
+        <f t="shared" si="3"/>
         <v>TELB1</v>
       </c>
     </row>
     <row r="15" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B15" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C15" cm="1">
@@ -14777,7 +14769,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>592</v>
@@ -14876,16 +14868,16 @@
         <v>1</v>
       </c>
       <c r="AK15" s="69" t="str">
-        <f>MID(E15,5,LEN(E15)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACIQ1</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B16" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C16" cm="1">
@@ -14893,7 +14885,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>357</v>
@@ -14992,16 +14984,16 @@
         <v>1</v>
       </c>
       <c r="AK16" s="69" t="str">
-        <f>MID(E16,5,LEN(E16)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACNO1</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B17" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C17" cm="1">
@@ -15009,13 +15001,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -15108,13 +15100,13 @@
         <v>1</v>
       </c>
       <c r="AK17" s="69" t="str">
-        <f>MID(E17,5,LEN(E17)-4)</f>
+        <f t="shared" si="3"/>
         <v>ANCO1</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C18" cm="1">
@@ -15122,13 +15114,13 @@
         <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>848</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
@@ -15221,13 +15213,13 @@
         <v>0</v>
       </c>
       <c r="AK18" s="69" t="str">
-        <f>MID(E18,5,LEN(E18)-4)</f>
+        <f t="shared" si="3"/>
         <v>TACH2</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C19" cm="1">
@@ -15235,7 +15227,7 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>706</v>
@@ -15334,16 +15326,16 @@
         <v>0.99839999999999995</v>
       </c>
       <c r="AK19" s="69" t="str">
-        <f>MID(E19,5,LEN(E19)-4)</f>
+        <f t="shared" si="3"/>
         <v>AAMB2</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B20" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C20" cm="1">
@@ -15351,13 +15343,13 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>398</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -15450,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="AK20" s="69" t="str">
-        <f>MID(E20,5,LEN(E20)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACHA1</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B21" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C21" cm="1">
@@ -15467,7 +15459,7 @@
         <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>895</v>
@@ -15566,13 +15558,13 @@
         <v>0</v>
       </c>
       <c r="AK21" s="69" t="str">
-        <f>MID(E21,5,LEN(E21)-4)</f>
+        <f t="shared" si="3"/>
         <v>SASA2</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C22" cm="1">
@@ -15580,7 +15572,7 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>252</v>
@@ -15679,13 +15671,13 @@
         <v>1</v>
       </c>
       <c r="AK22" s="69" t="str">
-        <f>MID(E22,5,LEN(E22)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACIP1</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C23" cm="1">
@@ -15693,7 +15685,7 @@
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>561</v>
@@ -15792,13 +15784,13 @@
         <v>1</v>
       </c>
       <c r="AK23" s="69" t="str">
-        <f>MID(E23,5,LEN(E23)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACIP2</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C24" cm="1">
@@ -15806,13 +15798,13 @@
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>977</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="G24" s="1">
         <v>2</v>
@@ -15903,13 +15895,13 @@
         <v>0</v>
       </c>
       <c r="AK24" s="69" t="str">
-        <f>MID(E24,5,LEN(E24)-4)</f>
+        <f t="shared" si="3"/>
         <v>SALV2</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C25" cm="1">
@@ -15917,7 +15909,7 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>237</v>
@@ -16016,13 +16008,13 @@
         <v>1</v>
       </c>
       <c r="AK25" s="69" t="str">
-        <f>MID(E25,5,LEN(E25)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACMA1</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C26" cm="1">
@@ -16030,7 +16022,7 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>607</v>
@@ -16129,13 +16121,13 @@
         <v>1</v>
       </c>
       <c r="AK26" s="69" t="str">
-        <f>MID(E26,5,LEN(E26)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACMA2</v>
       </c>
     </row>
     <row r="27" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C27" cm="1">
@@ -16143,13 +16135,13 @@
         <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>577</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -16242,16 +16234,16 @@
         <v>1</v>
       </c>
       <c r="AK27" s="69" t="str">
-        <f>MID(E27,5,LEN(E27)-4)</f>
+        <f t="shared" si="3"/>
         <v>AURA1</v>
       </c>
     </row>
     <row r="28" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B28" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C28" cm="1">
@@ -16259,7 +16251,7 @@
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>230</v>
@@ -16358,16 +16350,16 @@
         <v>1</v>
       </c>
       <c r="AK28" s="69" t="str">
-        <f>MID(E28,5,LEN(E28)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACSU1</v>
       </c>
     </row>
     <row r="29" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B29" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C29" cm="1">
@@ -16375,7 +16367,7 @@
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>737</v>
@@ -16474,13 +16466,13 @@
         <v>1</v>
       </c>
       <c r="AK29" s="69" t="str">
-        <f>MID(E29,5,LEN(E29)-4)</f>
+        <f t="shared" si="3"/>
         <v>ACSU2</v>
       </c>
     </row>
     <row r="30" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C30" cm="1">
@@ -16488,7 +16480,7 @@
         <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>61</v>
@@ -16587,16 +16579,16 @@
         <v>1</v>
       </c>
       <c r="AK30" s="69" t="str">
-        <f>MID(E30,5,LEN(E30)-4)</f>
+        <f t="shared" si="3"/>
         <v>ADAI1</v>
       </c>
     </row>
     <row r="31" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B31" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C31" cm="1">
@@ -16604,7 +16596,7 @@
         <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>488</v>
@@ -16703,13 +16695,13 @@
         <v>1</v>
       </c>
       <c r="AK31" s="69" t="str">
-        <f>MID(E31,5,LEN(E31)-4)</f>
+        <f t="shared" si="3"/>
         <v>ADAI2</v>
       </c>
     </row>
     <row r="32" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C32" cm="1">
@@ -16717,7 +16709,7 @@
         <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>635</v>
@@ -16816,16 +16808,16 @@
         <v>1</v>
       </c>
       <c r="AK32" s="69" t="str">
-        <f>MID(E32,5,LEN(E32)-4)</f>
+        <f t="shared" si="3"/>
         <v>ADAI3</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B33" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C33" cm="1">
@@ -16833,7 +16825,7 @@
         <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>745</v>
@@ -16932,13 +16924,13 @@
         <v>1</v>
       </c>
       <c r="AK33" s="69" t="str">
-        <f>MID(E33,5,LEN(E33)-4)</f>
+        <f t="shared" si="3"/>
         <v>ADAI4</v>
       </c>
     </row>
     <row r="34" spans="1:37" ht="147.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="C34" cm="1">
@@ -16946,13 +16938,13 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>180</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -17045,13 +17037,13 @@
         <v>1</v>
       </c>
       <c r="AK34" s="69" t="str">
-        <f>MID(E34,5,LEN(E34)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALFS1</v>
       </c>
     </row>
     <row r="35" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B35:B66" si="4">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C35" cm="1">
@@ -17059,13 +17051,13 @@
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>643</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
@@ -17158,13 +17150,13 @@
         <v>1</v>
       </c>
       <c r="AK35" s="69" t="str">
-        <f>MID(E35,5,LEN(E35)-4)</f>
+        <f t="shared" ref="AK35:AK66" si="5">MID(E35,5,LEN(E35)-4)</f>
         <v>ALFS2</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C36" cm="1">
@@ -17172,10 +17164,10 @@
         <v>136</v>
       </c>
       <c r="D36" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E36" s="56" t="s">
-        <v>1744</v>
+        <v>1992</v>
       </c>
       <c r="F36" s="60" t="s">
         <v>1736</v>
@@ -17185,7 +17177,7 @@
         <v>1736</v>
       </c>
       <c r="I36" s="72" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="J36" s="57" t="s">
         <v>36</v>
@@ -17217,7 +17209,7 @@
       <c r="Y36" s="58"/>
       <c r="Z36" s="57"/>
       <c r="AA36" s="57" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AB36" s="57"/>
       <c r="AC36" s="58">
@@ -17231,16 +17223,16 @@
       <c r="AI36" s="22"/>
       <c r="AJ36" s="23"/>
       <c r="AK36" s="69" t="str">
-        <f>MID(E36,5,LEN(E36)-4)</f>
-        <v>RTCC</v>
+        <f t="shared" si="5"/>
+        <v>RTCC1</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B37" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C37" cm="1">
@@ -17248,7 +17240,7 @@
         <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>187</v>
@@ -17347,16 +17339,16 @@
         <v>1</v>
       </c>
       <c r="AK37" s="69" t="str">
-        <f>MID(E37,5,LEN(E37)-4)</f>
+        <f t="shared" si="5"/>
         <v>ALOA1</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B38" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C38" cm="1">
@@ -17364,7 +17356,7 @@
         <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>584</v>
@@ -17463,13 +17455,13 @@
         <v>1</v>
       </c>
       <c r="AK38" s="69" t="str">
-        <f>MID(E38,5,LEN(E38)-4)</f>
+        <f t="shared" si="5"/>
         <v>ALOA2</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C39" cm="1">
@@ -17477,10 +17469,10 @@
         <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E39" s="56" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="F39" s="60" t="s">
         <v>1735</v>
@@ -17492,7 +17484,7 @@
         <v>1735</v>
       </c>
       <c r="I39" s="57" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="J39" s="57" t="s">
         <v>36</v>
@@ -17524,7 +17516,7 @@
       <c r="Y39" s="58"/>
       <c r="Z39" s="57"/>
       <c r="AA39" s="3" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="AB39" s="57"/>
       <c r="AC39" s="58">
@@ -17538,13 +17530,13 @@
       <c r="AI39" s="22"/>
       <c r="AJ39" s="23"/>
       <c r="AK39" s="69" t="str">
-        <f>MID(E39,5,LEN(E39)-4)</f>
+        <f t="shared" si="5"/>
         <v>RPMO1</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C40" cm="1">
@@ -17552,7 +17544,7 @@
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>760</v>
@@ -17651,13 +17643,13 @@
         <v>769</v>
       </c>
       <c r="AK40" s="69" t="str">
-        <f>MID(E40,5,LEN(E40)-4)</f>
+        <f t="shared" si="5"/>
         <v>RNAH1</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C41" cm="1">
@@ -17665,7 +17657,7 @@
         <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>524</v>
@@ -17764,13 +17756,13 @@
         <v>1</v>
       </c>
       <c r="AK41" s="69" t="str">
-        <f>MID(E41,5,LEN(E41)-4)</f>
+        <f t="shared" si="5"/>
         <v>AVAM2</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C42" cm="1">
@@ -17778,13 +17770,13 @@
         <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>341</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -17877,13 +17869,13 @@
         <v>1</v>
       </c>
       <c r="AK42" s="69" t="str">
-        <f>MID(E42,5,LEN(E42)-4)</f>
+        <f t="shared" si="5"/>
         <v>ARAT1</v>
       </c>
     </row>
     <row r="43" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C43" cm="1">
@@ -17891,13 +17883,13 @@
         <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>630</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -17990,13 +17982,13 @@
         <v>0</v>
       </c>
       <c r="AK43" s="69" t="str">
-        <f>MID(E43,5,LEN(E43)-4)</f>
+        <f t="shared" si="5"/>
         <v>RLOA1</v>
       </c>
     </row>
     <row r="44" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C44" cm="1">
@@ -18004,13 +17996,13 @@
         <v>132</v>
       </c>
       <c r="D44" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>770</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="G44" s="1">
         <v>2</v>
@@ -18101,13 +18093,13 @@
         <v>777</v>
       </c>
       <c r="AK44" s="69" t="str">
-        <f>MID(E44,5,LEN(E44)-4)</f>
+        <f t="shared" si="5"/>
         <v>RLOA2</v>
       </c>
     </row>
     <row r="45" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C45" cm="1">
@@ -18115,7 +18107,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>495</v>
@@ -18214,13 +18206,13 @@
         <v>1</v>
       </c>
       <c r="AK45" s="69" t="str">
-        <f>MID(E45,5,LEN(E45)-4)</f>
+        <f t="shared" si="5"/>
         <v>ATEP2</v>
       </c>
     </row>
     <row r="46" spans="1:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C46" cm="1">
@@ -18228,7 +18220,7 @@
         <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>681</v>
@@ -18327,13 +18319,13 @@
         <v>1</v>
       </c>
       <c r="AK46" s="69" t="str">
-        <f>MID(E46,5,LEN(E46)-4)</f>
+        <f t="shared" si="5"/>
         <v>ATEP3</v>
       </c>
     </row>
     <row r="47" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C47" cm="1">
@@ -18341,7 +18333,7 @@
         <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>808</v>
@@ -18440,13 +18432,13 @@
         <v>1</v>
       </c>
       <c r="AK47" s="69" t="str">
-        <f>MID(E47,5,LEN(E47)-4)</f>
+        <f t="shared" si="5"/>
         <v>ATEP4</v>
       </c>
     </row>
     <row r="48" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C48" cm="1">
@@ -18454,13 +18446,13 @@
         <v>129</v>
       </c>
       <c r="D48" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>839</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -18553,13 +18545,13 @@
         <v>847</v>
       </c>
       <c r="AK48" s="69" t="str">
-        <f>MID(E48,5,LEN(E48)-4)</f>
+        <f t="shared" si="5"/>
         <v>RAUS1</v>
       </c>
     </row>
     <row r="49" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C49" cm="1">
@@ -18567,7 +18559,7 @@
         <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>287</v>
@@ -18666,13 +18658,13 @@
         <v>1</v>
       </c>
       <c r="AK49" s="69" t="str">
-        <f>MID(E49,5,LEN(E49)-4)</f>
+        <f t="shared" si="5"/>
         <v>AVES1</v>
       </c>
     </row>
     <row r="50" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C50" cm="1">
@@ -18680,7 +18672,7 @@
         <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>316</v>
@@ -18779,13 +18771,13 @@
         <v>1</v>
       </c>
       <c r="AK50" s="69" t="str">
-        <f>MID(E50,5,LEN(E50)-4)</f>
+        <f t="shared" si="5"/>
         <v>AVNP1</v>
       </c>
     </row>
     <row r="51" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C51" cm="1">
@@ -18793,7 +18785,7 @@
         <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>51</v>
@@ -18892,13 +18884,13 @@
         <v>1</v>
       </c>
       <c r="AK51" s="69" t="str">
-        <f>MID(E51,5,LEN(E51)-4)</f>
+        <f t="shared" si="5"/>
         <v>CDMA1</v>
       </c>
     </row>
     <row r="52" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C52" cm="1">
@@ -18906,13 +18898,13 @@
         <v>37</v>
       </c>
       <c r="D52" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -19005,13 +18997,13 @@
         <v>1</v>
       </c>
       <c r="AK52" s="69" t="str">
-        <f>MID(E52,5,LEN(E52)-4)</f>
+        <f t="shared" si="5"/>
         <v>CHCO1</v>
       </c>
     </row>
     <row r="53" spans="2:37" ht="242.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C53" cm="1">
@@ -19019,20 +19011,20 @@
         <v>126</v>
       </c>
       <c r="D53" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E53" s="71" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="G53" s="57"/>
       <c r="H53" s="60" t="s">
         <v>1737</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="J53" s="57" t="s">
         <v>36</v>
@@ -19066,7 +19058,7 @@
       <c r="Y53" s="58"/>
       <c r="Z53" s="57"/>
       <c r="AA53" s="57" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="AB53" s="57"/>
       <c r="AC53" s="58">
@@ -19082,13 +19074,13 @@
       <c r="AI53" s="22"/>
       <c r="AJ53" s="23"/>
       <c r="AK53" s="69" t="str">
-        <f>MID(E53,5,LEN(E53)-4)</f>
+        <f t="shared" si="5"/>
         <v>RBPM2</v>
       </c>
     </row>
     <row r="54" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C54" cm="1">
@@ -19096,7 +19088,7 @@
         <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>98</v>
@@ -19195,13 +19187,13 @@
         <v>1</v>
       </c>
       <c r="AK54" s="69" t="str">
-        <f>MID(E54,5,LEN(E54)-4)</f>
+        <f t="shared" si="5"/>
         <v>CNPU1</v>
       </c>
     </row>
     <row r="55" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C55" cm="1">
@@ -19209,7 +19201,7 @@
         <v>42</v>
       </c>
       <c r="D55" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>666</v>
@@ -19308,13 +19300,13 @@
         <v>1</v>
       </c>
       <c r="AK55" s="69" t="str">
-        <f>MID(E55,5,LEN(E55)-4)</f>
+        <f t="shared" si="5"/>
         <v>CFLL1</v>
       </c>
     </row>
     <row r="56" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C56" cm="1">
@@ -19322,7 +19314,7 @@
         <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="E56" s="44" t="s">
         <v>1007</v>
@@ -19419,13 +19411,13 @@
         <v>0</v>
       </c>
       <c r="AK56" s="69" t="str">
-        <f>MID(E56,5,LEN(E56)-4)</f>
+        <f t="shared" si="5"/>
         <v>NARA2</v>
       </c>
     </row>
     <row r="57" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C57" cm="1">
@@ -19433,13 +19425,13 @@
         <v>43</v>
       </c>
       <c r="D57" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>600</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -19532,13 +19524,13 @@
         <v>1</v>
       </c>
       <c r="AK57" s="70" t="str">
-        <f>MID(E57,5,LEN(E57)-4)</f>
+        <f t="shared" si="5"/>
         <v>COCA1</v>
       </c>
     </row>
     <row r="58" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C58" cm="1">
@@ -19546,7 +19538,7 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>516</v>
@@ -19645,13 +19637,13 @@
         <v>1</v>
       </c>
       <c r="AK58" s="69" t="str">
-        <f>MID(E58,5,LEN(E58)-4)</f>
+        <f t="shared" si="5"/>
         <v>CMVR1</v>
       </c>
     </row>
     <row r="59" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C59" cm="1">
@@ -19659,13 +19651,13 @@
         <v>45</v>
       </c>
       <c r="D59" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>213</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -19758,13 +19750,13 @@
         <v>1</v>
       </c>
       <c r="AK59" s="69" t="str">
-        <f>MID(E59,5,LEN(E59)-4)</f>
+        <f t="shared" si="5"/>
         <v>COTE1</v>
       </c>
     </row>
     <row r="60" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C60" cm="1">
@@ -19772,7 +19764,7 @@
         <v>48</v>
       </c>
       <c r="D60" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>147</v>
@@ -19871,13 +19863,13 @@
         <v>1</v>
       </c>
       <c r="AK60" s="69" t="str">
-        <f>MID(E60,5,LEN(E60)-4)</f>
+        <f t="shared" si="5"/>
         <v>ISVV1</v>
       </c>
     </row>
     <row r="61" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C61" cm="1">
@@ -19885,7 +19877,7 @@
         <v>123</v>
       </c>
       <c r="D61" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E61" s="20" t="s">
         <v>969</v>
@@ -19984,13 +19976,13 @@
         <v>0</v>
       </c>
       <c r="AK61" s="69" t="str">
-        <f>MID(E61,5,LEN(E61)-4)</f>
+        <f t="shared" si="5"/>
         <v>ORSS1</v>
       </c>
     </row>
     <row r="62" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C62" cm="1">
@@ -19998,13 +19990,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>172</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -20097,13 +20089,13 @@
         <v>1</v>
       </c>
       <c r="AK62" s="69" t="str">
-        <f>MID(E62,5,LEN(E62)-4)</f>
+        <f t="shared" si="5"/>
         <v>LVLS1</v>
       </c>
     </row>
     <row r="63" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C63" cm="1">
@@ -20111,7 +20103,7 @@
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>406</v>
@@ -20210,13 +20202,13 @@
         <v>1</v>
       </c>
       <c r="AK63" s="69" t="str">
-        <f>MID(E63,5,LEN(E63)-4)</f>
+        <f t="shared" si="5"/>
         <v>CSJS1</v>
       </c>
     </row>
     <row r="64" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C64" cm="1">
@@ -20224,7 +20216,7 @@
         <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>471</v>
@@ -20323,13 +20315,13 @@
         <v>1</v>
       </c>
       <c r="AK64" s="69" t="str">
-        <f>MID(E64,5,LEN(E64)-4)</f>
+        <f t="shared" si="5"/>
         <v>CTSR1</v>
       </c>
     </row>
     <row r="65" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C65" cm="1">
@@ -20337,7 +20329,7 @@
         <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>455</v>
@@ -20436,13 +20428,13 @@
         <v>1</v>
       </c>
       <c r="AK65" s="69" t="str">
-        <f>MID(E65,5,LEN(E65)-4)</f>
+        <f t="shared" si="5"/>
         <v>CVSR1</v>
       </c>
     </row>
     <row r="66" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="C66" cm="1">
@@ -20450,13 +20442,13 @@
         <v>54</v>
       </c>
       <c r="D66" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>431</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -20549,13 +20541,13 @@
         <v>1</v>
       </c>
       <c r="AK66" s="69" t="str">
-        <f>MID(E66,5,LEN(E66)-4)</f>
+        <f t="shared" si="5"/>
         <v>ECVI1</v>
       </c>
     </row>
     <row r="67" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B67:B98" si="6">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C67" cm="1">
@@ -20563,13 +20555,13 @@
         <v>121</v>
       </c>
       <c r="D67" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>932</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -20662,13 +20654,13 @@
         <v>0</v>
       </c>
       <c r="AK67" s="69" t="str">
-        <f>MID(E67,5,LEN(E67)-4)</f>
+        <f t="shared" ref="AK67:AK98" si="7">MID(E67,5,LEN(E67)-4)</f>
         <v>INAC1</v>
       </c>
     </row>
     <row r="68" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C68" cm="1">
@@ -20676,7 +20668,7 @@
         <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>390</v>
@@ -20775,13 +20767,13 @@
         <v>1</v>
       </c>
       <c r="AK68" s="69" t="str">
-        <f>MID(E68,5,LEN(E68)-4)</f>
+        <f t="shared" si="7"/>
         <v>EIMC1</v>
       </c>
     </row>
     <row r="69" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C69" cm="1">
@@ -20789,7 +20781,7 @@
         <v>120</v>
       </c>
       <c r="D69" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>688</v>
@@ -20888,13 +20880,13 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="AK69" s="69" t="str">
-        <f>MID(E69,5,LEN(E69)-4)</f>
+        <f t="shared" si="7"/>
         <v>HSSG1</v>
       </c>
     </row>
     <row r="70" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C70" cm="1">
@@ -20902,13 +20894,13 @@
         <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>887</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -21001,13 +20993,13 @@
         <v>894</v>
       </c>
       <c r="AK70" s="69" t="str">
-        <f>MID(E70,5,LEN(E70)-4)</f>
+        <f t="shared" si="7"/>
         <v>HRRL1</v>
       </c>
     </row>
     <row r="71" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C71" cm="1">
@@ -21015,13 +21007,13 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>902</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -21114,13 +21106,13 @@
         <v>0.14749999999999999</v>
       </c>
       <c r="AK71" s="69" t="str">
-        <f>MID(E71,5,LEN(E71)-4)</f>
+        <f t="shared" si="7"/>
         <v>HRQS1</v>
       </c>
     </row>
     <row r="72" spans="2:37" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C72" cm="1">
@@ -21128,7 +21120,7 @@
         <v>60</v>
       </c>
       <c r="D72" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>422</v>
@@ -21227,13 +21219,13 @@
         <v>1</v>
       </c>
       <c r="AK72" s="69" t="str">
-        <f>MID(E72,5,LEN(E72)-4)</f>
+        <f t="shared" si="7"/>
         <v>ETPO1</v>
       </c>
     </row>
     <row r="73" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C73" cm="1">
@@ -21241,7 +21233,7 @@
         <v>98</v>
       </c>
       <c r="D73" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>463</v>
@@ -21340,13 +21332,13 @@
         <v>1</v>
       </c>
       <c r="AK73" s="69" t="str">
-        <f>MID(E73,5,LEN(E73)-4)</f>
+        <f t="shared" si="7"/>
         <v>ETTT1</v>
       </c>
     </row>
     <row r="74" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C74" cm="1">
@@ -21354,13 +21346,13 @@
         <v>110</v>
       </c>
       <c r="D74" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>917</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -21453,13 +21445,13 @@
         <v>0.2389</v>
       </c>
       <c r="AK74" s="69" t="str">
-        <f>MID(E74,5,LEN(E74)-4)</f>
+        <f t="shared" si="7"/>
         <v>HRQQ1</v>
       </c>
     </row>
     <row r="75" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C75" cm="1">
@@ -21467,13 +21459,13 @@
         <v>109</v>
       </c>
       <c r="D75" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>939</v>
       </c>
       <c r="F75" s="57" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -21564,13 +21556,13 @@
         <v>0</v>
       </c>
       <c r="AK75" s="69" t="str">
-        <f>MID(E75,5,LEN(E75)-4)</f>
+        <f t="shared" si="7"/>
         <v>HROG1</v>
       </c>
     </row>
     <row r="76" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C76" cm="1">
@@ -21578,13 +21570,13 @@
         <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>863</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -21677,13 +21669,13 @@
         <v>871</v>
       </c>
       <c r="AK76" s="69" t="str">
-        <f>MID(E76,5,LEN(E76)-4)</f>
+        <f t="shared" si="7"/>
         <v>HRMA1</v>
       </c>
     </row>
     <row r="77" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C77" cm="1">
@@ -21691,13 +21683,13 @@
         <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>879</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -21790,13 +21782,13 @@
         <v>886</v>
       </c>
       <c r="AK77" s="69" t="str">
-        <f>MID(E77,5,LEN(E77)-4)</f>
+        <f t="shared" si="7"/>
         <v>HRBB1</v>
       </c>
     </row>
     <row r="78" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C78" cm="1">
@@ -21804,7 +21796,7 @@
         <v>100</v>
       </c>
       <c r="D78" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>954</v>
@@ -21903,13 +21895,13 @@
         <v>0</v>
       </c>
       <c r="AK78" s="69" t="str">
-        <f>MID(E78,5,LEN(E78)-4)</f>
+        <f t="shared" si="7"/>
         <v>HINN1</v>
       </c>
     </row>
     <row r="79" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C79" cm="1">
@@ -21917,13 +21909,13 @@
         <v>99</v>
       </c>
       <c r="D79" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>872</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -22016,13 +22008,13 @@
         <v>0.82579999999999998</v>
       </c>
       <c r="AK79" s="69" t="str">
-        <f>MID(E79,5,LEN(E79)-4)</f>
+        <f t="shared" si="7"/>
         <v>HBUP1</v>
       </c>
     </row>
     <row r="80" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C80" cm="1">
@@ -22030,13 +22022,13 @@
         <v>59</v>
       </c>
       <c r="D80" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -22129,13 +22121,13 @@
         <v>0</v>
       </c>
       <c r="AK80" s="69" t="str">
-        <f>MID(E80,5,LEN(E80)-4)</f>
+        <f t="shared" si="7"/>
         <v>EPUN1</v>
       </c>
     </row>
     <row r="81" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C81" cm="1">
@@ -22143,13 +22135,13 @@
         <v>58</v>
       </c>
       <c r="D81" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E81" s="45" t="s">
         <v>1026</v>
       </c>
       <c r="F81" s="45" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -22240,13 +22232,13 @@
         <v>0</v>
       </c>
       <c r="AK81" s="69" t="str">
-        <f>MID(E81,5,LEN(E81)-4)</f>
+        <f t="shared" si="7"/>
         <v>EPCO1</v>
       </c>
     </row>
     <row r="82" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C82" cm="1">
@@ -22254,7 +22246,7 @@
         <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>650</v>
@@ -22353,13 +22345,13 @@
         <v>1</v>
       </c>
       <c r="AK82" s="69" t="str">
-        <f>MID(E82,5,LEN(E82)-4)</f>
+        <f t="shared" si="7"/>
         <v>HSAN1</v>
       </c>
     </row>
     <row r="83" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C83" cm="1">
@@ -22367,7 +22359,7 @@
         <v>117</v>
       </c>
       <c r="D83" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>698</v>
@@ -22466,13 +22458,13 @@
         <v>1</v>
       </c>
       <c r="AK83" s="69" t="str">
-        <f>MID(E83,5,LEN(E83)-4)</f>
+        <f t="shared" si="7"/>
         <v>HSFB1</v>
       </c>
     </row>
     <row r="84" spans="1:37" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C84" cm="1">
@@ -22480,7 +22472,7 @@
         <v>119</v>
       </c>
       <c r="D84" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>532</v>
@@ -22579,13 +22571,13 @@
         <v>1</v>
       </c>
       <c r="AK84" s="69" t="str">
-        <f>MID(E84,5,LEN(E84)-4)</f>
+        <f t="shared" si="7"/>
         <v>HSMF1</v>
       </c>
     </row>
     <row r="85" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C85" cm="1">
@@ -22593,13 +22585,13 @@
         <v>57</v>
       </c>
       <c r="D85" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>785</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -22692,13 +22684,13 @@
         <v>0.21240000000000001</v>
       </c>
       <c r="AK85" s="1" t="str">
-        <f>MID(E85,5,LEN(E85)-4)</f>
+        <f t="shared" si="7"/>
         <v>ELPA1</v>
       </c>
     </row>
     <row r="86" spans="1:37" ht="148.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C86" cm="1">
@@ -22706,13 +22698,13 @@
         <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>261</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -22805,13 +22797,13 @@
         <v>0</v>
       </c>
       <c r="AK86" s="69" t="str">
-        <f>MID(E86,5,LEN(E86)-4)</f>
+        <f t="shared" si="7"/>
         <v>EEBA1</v>
       </c>
     </row>
     <row r="87" spans="1:37" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C87" cm="1">
@@ -22819,13 +22811,13 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>824</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="G87" s="1">
         <v>2</v>
@@ -22918,16 +22910,16 @@
         <v>831</v>
       </c>
       <c r="AK87" s="69" t="str">
-        <f>MID(E87,5,LEN(E87)-4)</f>
+        <f t="shared" si="7"/>
         <v>LVLS2</v>
       </c>
     </row>
     <row r="88" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B88" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C88" cm="1">
@@ -22935,13 +22927,13 @@
         <v>122</v>
       </c>
       <c r="D88" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>658</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -23034,13 +23026,13 @@
         <v>0.93169999999999997</v>
       </c>
       <c r="AK88" s="69" t="str">
-        <f>MID(E88,5,LEN(E88)-4)</f>
+        <f t="shared" si="7"/>
         <v>NPIB1</v>
       </c>
     </row>
     <row r="89" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C89" cm="1">
@@ -23048,7 +23040,7 @@
         <v>48</v>
       </c>
       <c r="D89" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E89" s="57" t="s">
         <v>962</v>
@@ -23145,13 +23137,13 @@
         <v>0</v>
       </c>
       <c r="AK89" s="69" t="str">
-        <f>MID(E89,5,LEN(E89)-4)</f>
+        <f t="shared" si="7"/>
         <v>ISVV2</v>
       </c>
     </row>
     <row r="90" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C90" cm="1">
@@ -23159,7 +23151,7 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>554</v>
@@ -23258,13 +23250,13 @@
         <v>1</v>
       </c>
       <c r="AK90" s="69" t="str">
-        <f>MID(E90,5,LEN(E90)-4)</f>
+        <f t="shared" si="7"/>
         <v>NARA1</v>
       </c>
     </row>
     <row r="91" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C91" cm="1">
@@ -23272,7 +23264,7 @@
         <v>41</v>
       </c>
       <c r="D91" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>729</v>
@@ -23371,13 +23363,13 @@
         <v>736</v>
       </c>
       <c r="AK91" s="69" t="str">
-        <f>MID(E91,5,LEN(E91)-4)</f>
+        <f t="shared" si="7"/>
         <v>CNPU2</v>
       </c>
     </row>
     <row r="92" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C92" cm="1">
@@ -23385,13 +23377,13 @@
         <v>125</v>
       </c>
       <c r="D92" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>547</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -23484,13 +23476,13 @@
         <v>1</v>
       </c>
       <c r="AK92" s="69" t="str">
-        <f>MID(E92,5,LEN(E92)-4)</f>
+        <f t="shared" si="7"/>
         <v>PMPA1</v>
       </c>
     </row>
     <row r="93" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C93" cm="1">
@@ -23498,13 +23490,13 @@
         <v>126</v>
       </c>
       <c r="D93" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>195</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -23597,13 +23589,13 @@
         <v>1</v>
       </c>
       <c r="AK93" s="70" t="str">
-        <f>MID(E93,5,LEN(E93)-4)</f>
+        <f t="shared" si="7"/>
         <v>RBPM1</v>
       </c>
     </row>
     <row r="94" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C94" cm="1">
@@ -23611,13 +23603,13 @@
         <v>37</v>
       </c>
       <c r="D94" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>946</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="G94" s="1">
         <v>2</v>
@@ -23710,13 +23702,13 @@
         <v>0</v>
       </c>
       <c r="AK94" s="69" t="str">
-        <f>MID(E94,5,LEN(E94)-4)</f>
+        <f t="shared" si="7"/>
         <v>CHCO2</v>
       </c>
     </row>
     <row r="95" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C95" cm="1">
@@ -23724,7 +23716,7 @@
         <v>175</v>
       </c>
       <c r="D95" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>414</v>
@@ -23823,13 +23815,13 @@
         <v>1</v>
       </c>
       <c r="AK95" s="1" t="str">
-        <f>MID(E95,5,LEN(E95)-4)</f>
+        <f t="shared" si="7"/>
         <v>PCIS1</v>
       </c>
     </row>
     <row r="96" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C96" cm="1">
@@ -23837,7 +23829,7 @@
         <v>128</v>
       </c>
       <c r="D96" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>324</v>
@@ -23936,13 +23928,13 @@
         <v>1</v>
       </c>
       <c r="AK96" s="1" t="str">
-        <f>MID(E96,5,LEN(E96)-4)</f>
+        <f t="shared" si="7"/>
         <v>RITP1</v>
       </c>
     </row>
     <row r="97" spans="2:37" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B97" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C97" cm="1">
@@ -23950,7 +23942,7 @@
         <v>178</v>
       </c>
       <c r="D97" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>305</v>
@@ -24049,13 +24041,13 @@
         <v>1</v>
       </c>
       <c r="AK97" s="69" t="str">
-        <f>MID(E97,5,LEN(E97)-4)</f>
+        <f t="shared" si="7"/>
         <v>PP1G1</v>
       </c>
     </row>
     <row r="98" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="C98" cm="1">
@@ -24063,7 +24055,7 @@
         <v>33</v>
       </c>
       <c r="D98" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>72</v>
@@ -24162,13 +24154,13 @@
         <v>1</v>
       </c>
       <c r="AK98" s="69" t="str">
-        <f>MID(E98,5,LEN(E98)-4)</f>
+        <f t="shared" si="7"/>
         <v>ATEP1</v>
       </c>
     </row>
     <row r="99" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B99:B124" si="8">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C99" cm="1">
@@ -24176,7 +24168,7 @@
         <v>32</v>
       </c>
       <c r="D99" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>990</v>
@@ -24273,13 +24265,13 @@
         <v>0</v>
       </c>
       <c r="AK99" s="1" t="str">
-        <f>MID(E99,5,LEN(E99)-4)</f>
+        <f t="shared" ref="AK99:AK124" si="9">MID(E99,5,LEN(E99)-4)</f>
         <v>ARNO1</v>
       </c>
     </row>
     <row r="100" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C100" cm="1">
@@ -24287,7 +24279,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>107</v>
@@ -24386,13 +24378,13 @@
         <v>1</v>
       </c>
       <c r="AK100" s="69" t="str">
-        <f>MID(E100,5,LEN(E100)-4)</f>
+        <f t="shared" si="9"/>
         <v>AVAM1</v>
       </c>
     </row>
     <row r="101" spans="2:37" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C101" cm="1">
@@ -24400,7 +24392,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>909</v>
@@ -24499,13 +24491,13 @@
         <v>0.55930000000000002</v>
       </c>
       <c r="AK101" s="69" t="str">
-        <f>MID(E101,5,LEN(E101)-4)</f>
+        <f t="shared" si="9"/>
         <v>AVAM3</v>
       </c>
     </row>
     <row r="102" spans="2:37" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C102" cm="1">
@@ -24513,7 +24505,7 @@
         <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>439</v>
@@ -24612,13 +24604,13 @@
         <v>1</v>
       </c>
       <c r="AK102" s="1" t="str">
-        <f>MID(E102,5,LEN(E102)-4)</f>
+        <f t="shared" si="9"/>
         <v>PTLA1</v>
       </c>
     </row>
     <row r="103" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C103" cm="1">
@@ -24626,7 +24618,7 @@
         <v>28</v>
       </c>
       <c r="D103" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>924</v>
@@ -24725,13 +24717,13 @@
         <v>0</v>
       </c>
       <c r="AK103" s="69" t="str">
-        <f>MID(E103,5,LEN(E103)-4)</f>
+        <f t="shared" si="9"/>
         <v>ALOA3</v>
       </c>
     </row>
     <row r="104" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C104" cm="1">
@@ -24739,13 +24731,13 @@
         <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>856</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="G104" s="1">
         <v>3</v>
@@ -24838,13 +24830,13 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="AK104" s="69" t="str">
-        <f>MID(E104,5,LEN(E104)-4)</f>
+        <f t="shared" si="9"/>
         <v>ALFS3</v>
       </c>
     </row>
     <row r="105" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C105" cm="1">
@@ -24852,13 +24844,13 @@
         <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>832</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="G105" s="1">
         <v>2</v>
@@ -24951,13 +24943,13 @@
         <v>1</v>
       </c>
       <c r="AK105" s="69" t="str">
-        <f>MID(E105,5,LEN(E105)-4)</f>
+        <f t="shared" si="9"/>
         <v>ACHA2</v>
       </c>
     </row>
     <row r="106" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C106" cm="1">
@@ -24965,7 +24957,7 @@
         <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>204</v>
@@ -25064,13 +25056,13 @@
         <v>1</v>
       </c>
       <c r="AK106" s="69" t="str">
-        <f>MID(E106,5,LEN(E106)-4)</f>
+        <f t="shared" si="9"/>
         <v>AAMB1</v>
       </c>
     </row>
     <row r="107" spans="2:37" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C107" cm="1">
@@ -25078,13 +25070,13 @@
         <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>983</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="G107" s="1">
         <v>2</v>
@@ -25177,13 +25169,13 @@
         <v>0</v>
       </c>
       <c r="AK107" s="69" t="str">
-        <f>MID(E107,5,LEN(E107)-4)</f>
+        <f t="shared" si="9"/>
         <v>ANCO2</v>
       </c>
     </row>
     <row r="108" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C108" cm="1">
@@ -25191,7 +25183,7 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>792</v>
@@ -25290,13 +25282,13 @@
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="AK108" s="1" t="str">
-        <f>MID(E108,5,LEN(E108)-4)</f>
+        <f t="shared" si="9"/>
         <v>67CV1</v>
       </c>
     </row>
     <row r="109" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C109" cm="1">
@@ -25304,7 +25296,7 @@
         <v>143</v>
       </c>
       <c r="D109" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>279</v>
@@ -25403,13 +25395,13 @@
         <v>1</v>
       </c>
       <c r="AK109" s="69" t="str">
-        <f>MID(E109,5,LEN(E109)-4)</f>
+        <f t="shared" si="9"/>
         <v>RVLC1</v>
       </c>
     </row>
     <row r="110" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C110" cm="1">
@@ -25417,13 +25409,13 @@
         <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -25516,13 +25508,13 @@
         <v>1</v>
       </c>
       <c r="AK110" s="69" t="str">
-        <f>MID(E110,5,LEN(E110)-4)</f>
+        <f t="shared" si="9"/>
         <v>SALV1</v>
       </c>
     </row>
     <row r="111" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C111" cm="1">
@@ -25530,7 +25522,7 @@
         <v>10</v>
       </c>
       <c r="D111" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>540</v>
@@ -25629,13 +25621,13 @@
         <v>0</v>
       </c>
       <c r="AK111" s="70" t="str">
-        <f>MID(E111,5,LEN(E111)-4)</f>
+        <f t="shared" si="9"/>
         <v>66RF1</v>
       </c>
     </row>
     <row r="112" spans="2:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C112" cm="1">
@@ -25643,7 +25635,7 @@
         <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E112" s="57" t="s">
         <v>89</v>
@@ -25742,13 +25734,13 @@
         <v>1</v>
       </c>
       <c r="AK112" s="69" t="str">
-        <f>MID(E112,5,LEN(E112)-4)</f>
+        <f t="shared" si="9"/>
         <v>SASA1</v>
       </c>
     </row>
     <row r="113" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C113" cm="1">
@@ -25756,7 +25748,7 @@
         <v>10</v>
       </c>
       <c r="D113" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>800</v>
@@ -25855,13 +25847,13 @@
         <v>807</v>
       </c>
       <c r="AK113" s="69" t="str">
-        <f>MID(E113,5,LEN(E113)-4)</f>
+        <f t="shared" si="9"/>
         <v>66RF2</v>
       </c>
     </row>
     <row r="114" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C114" cm="1">
@@ -25869,13 +25861,13 @@
         <v>149</v>
       </c>
       <c r="D114" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>221</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -25968,13 +25960,13 @@
         <v>1</v>
       </c>
       <c r="AK114" s="69" t="str">
-        <f>MID(E114,5,LEN(E114)-4)</f>
+        <f t="shared" si="9"/>
         <v>SATA1</v>
       </c>
     </row>
     <row r="115" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C115" cm="1">
@@ -25982,7 +25974,7 @@
         <v>154</v>
       </c>
       <c r="D115" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E115" s="57" t="s">
         <v>128</v>
@@ -26081,13 +26073,13 @@
         <v>1</v>
       </c>
       <c r="AK115" s="69" t="str">
-        <f>MID(E115,5,LEN(E115)-4)</f>
+        <f t="shared" si="9"/>
         <v>SCLA1</v>
       </c>
     </row>
     <row r="116" spans="1:37" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C116" cm="1">
@@ -26095,7 +26087,7 @@
         <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>270</v>
@@ -26194,13 +26186,13 @@
         <v>1</v>
       </c>
       <c r="AK116" s="69" t="str">
-        <f>MID(E116,5,LEN(E116)-4)</f>
+        <f t="shared" si="9"/>
         <v>SNSS1</v>
       </c>
     </row>
     <row r="117" spans="1:37" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C117" cm="1">
@@ -26208,13 +26200,13 @@
         <v>158</v>
       </c>
       <c r="D117" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>244</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="G117" s="1">
         <v>1</v>
@@ -26307,13 +26299,13 @@
         <v>1</v>
       </c>
       <c r="AK117" s="69" t="str">
-        <f>MID(E117,5,LEN(E117)-4)</f>
+        <f t="shared" si="9"/>
         <v>SOPN1</v>
       </c>
     </row>
     <row r="118" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C118" cm="1">
@@ -26321,13 +26313,13 @@
         <v>159</v>
       </c>
       <c r="D118" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="G118" s="1">
         <v>1</v>
@@ -26420,13 +26412,13 @@
         <v>1</v>
       </c>
       <c r="AK118" s="69" t="str">
-        <f>MID(E118,5,LEN(E118)-4)</f>
+        <f t="shared" si="9"/>
         <v>TACH1</v>
       </c>
     </row>
     <row r="119" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C119" cm="1">
@@ -26434,7 +26426,7 @@
         <v>7</v>
       </c>
       <c r="D119" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>502</v>
@@ -26533,13 +26525,13 @@
         <v>0</v>
       </c>
       <c r="AK119" s="1" t="str">
-        <f>MID(E119,5,LEN(E119)-4)</f>
+        <f t="shared" si="9"/>
         <v>60GR1</v>
       </c>
     </row>
     <row r="120" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C120" cm="1">
@@ -26547,13 +26539,13 @@
         <v>4</v>
       </c>
       <c r="D120" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>753</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="G120" s="1">
         <v>1</v>
@@ -26646,16 +26638,16 @@
         <v>0.2641</v>
       </c>
       <c r="AK120" s="69" t="str">
-        <f>MID(E120,5,LEN(E120)-4)</f>
+        <f t="shared" si="9"/>
         <v>2AVO1</v>
       </c>
     </row>
     <row r="121" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B121" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C121" cm="1">
@@ -26762,13 +26754,13 @@
         <v>1</v>
       </c>
       <c r="AK121" s="69" t="str">
-        <f>MID(E121,5,LEN(E121)-4)</f>
+        <f t="shared" si="9"/>
         <v>TEME1</v>
       </c>
     </row>
     <row r="122" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C122" cm="1">
@@ -26875,13 +26867,13 @@
         <v>1</v>
       </c>
       <c r="AK122" s="69" t="str">
-        <f>MID(E122,5,LEN(E122)-4)</f>
+        <f t="shared" si="9"/>
         <v>TEME2</v>
       </c>
     </row>
     <row r="123" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C123" cm="1">
@@ -26889,13 +26881,13 @@
         <v>162</v>
       </c>
       <c r="D123" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E123" s="21" t="s">
         <v>164</v>
       </c>
       <c r="F123" s="21" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="G123" s="1">
         <v>1</v>
@@ -26988,13 +26980,13 @@
         <v>1</v>
       </c>
       <c r="AK123" s="69" t="str">
-        <f>MID(E123,5,LEN(E123)-4)</f>
+        <f t="shared" si="9"/>
         <v>TERB1</v>
       </c>
     </row>
     <row r="124" spans="1:37" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="1">
-        <f>MAX($C$2:$C$128)</f>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
       <c r="C124" cm="1">
@@ -27002,13 +26994,13 @@
         <v>3</v>
       </c>
       <c r="D124" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E124" s="21" t="s">
         <v>816</v>
       </c>
       <c r="F124" s="21" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="G124" s="1">
         <v>1</v>
@@ -27101,13 +27093,13 @@
         <v>0</v>
       </c>
       <c r="AK124" s="69" t="str">
-        <f>MID(E124,5,LEN(E124)-4)</f>
+        <f t="shared" si="9"/>
         <v>21RG1</v>
       </c>
     </row>
     <row r="125" spans="1:37" ht="201.6" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
-        <f t="shared" ref="B98:B128" si="2">MAX($C$2:$C$128)</f>
+        <f t="shared" ref="B125:B128" si="10">MAX($C$2:$C$128)</f>
         <v>190</v>
       </c>
       <c r="C125" cm="1">
@@ -27115,13 +27107,13 @@
         <v>163</v>
       </c>
       <c r="D125" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>622</v>
       </c>
       <c r="F125" s="61" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="G125" s="1">
         <v>1</v>
@@ -27214,13 +27206,13 @@
         <v>1</v>
       </c>
       <c r="AK125" s="69" t="str">
-        <f t="shared" ref="AK98:AK128" si="3">MID(E125,5,LEN(E125)-4)</f>
+        <f t="shared" ref="AK125:AK128" si="11">MID(E125,5,LEN(E125)-4)</f>
         <v>VALS1</v>
       </c>
     </row>
     <row r="126" spans="1:37" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>190</v>
       </c>
       <c r="C126" cm="1">
@@ -27228,7 +27220,7 @@
         <v>164</v>
       </c>
       <c r="D126" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>296</v>
@@ -27327,16 +27319,16 @@
         <v>1</v>
       </c>
       <c r="AK126" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>VAME1</v>
       </c>
     </row>
     <row r="127" spans="1:37" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B127" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>190</v>
       </c>
       <c r="C127" cm="1">
@@ -27344,13 +27336,13 @@
         <v>168</v>
       </c>
       <c r="D127" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>508</v>
       </c>
       <c r="F127" s="61" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="G127" s="1">
         <v>1</v>
@@ -27443,13 +27435,13 @@
         <v>1</v>
       </c>
       <c r="AK127" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>VCAL1</v>
       </c>
     </row>
     <row r="128" spans="1:37" ht="259.2" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>190</v>
       </c>
       <c r="C128" cm="1">
@@ -27457,7 +27449,7 @@
         <v>174</v>
       </c>
       <c r="D128" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>447</v>
@@ -27556,7 +27548,7 @@
         <v>1</v>
       </c>
       <c r="AK128" s="69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>VVSK1</v>
       </c>
     </row>
@@ -34426,34 +34418,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B1" t="s">
         <v>1743</v>
       </c>
       <c r="C1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D1" s="84" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E1" s="84" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F1" s="85" t="s">
         <v>1908</v>
       </c>
-      <c r="E1" s="84" t="s">
-        <v>1959</v>
-      </c>
-      <c r="F1" s="85" t="s">
+      <c r="G1" s="85" t="s">
         <v>1909</v>
       </c>
-      <c r="G1" s="85" t="s">
+      <c r="H1" s="84" t="s">
         <v>1910</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="I1" s="84" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J1" s="84" t="s">
         <v>1911</v>
-      </c>
-      <c r="I1" s="84" t="s">
-        <v>1982</v>
-      </c>
-      <c r="J1" s="84" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -34466,28 +34458,28 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="E2" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F2" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G2" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G2" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H2" s="76">
         <v>811000000</v>
       </c>
       <c r="I2" s="76" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="J2" s="78" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -34500,25 +34492,25 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="F3" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G3" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G3" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H3" s="77">
         <v>160000000</v>
       </c>
       <c r="I3" s="77" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -34531,28 +34523,28 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E4" s="37" t="s">
         <v>866</v>
       </c>
       <c r="F4" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G4" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G4" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H4" s="77">
         <v>40000000</v>
       </c>
       <c r="I4" s="77" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="J4" s="78" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -34565,28 +34557,28 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F5" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G5" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G5" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H5" s="77">
         <v>3000000</v>
       </c>
       <c r="I5" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J5" s="78" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -34599,28 +34591,28 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>912</v>
       </c>
       <c r="F6" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G6" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G6" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H6" s="77">
         <v>950000000</v>
       </c>
       <c r="I6" s="77" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="J6" s="87" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -34633,28 +34625,28 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>912</v>
       </c>
       <c r="F7" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G7" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G7" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H7" s="77">
         <v>1877000000</v>
       </c>
       <c r="I7" s="77" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="J7" s="78" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -34670,25 +34662,25 @@
         <v>35</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G8" s="75" t="s">
         <v>1914</v>
       </c>
-      <c r="G8" s="75" t="s">
-        <v>1915</v>
-      </c>
       <c r="H8" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I8" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J8" s="88" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -34704,25 +34696,25 @@
         <v>41</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F9" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G9" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G9" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H9" s="77">
         <v>79000000</v>
       </c>
       <c r="I9" s="77" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="J9" s="78" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -34735,23 +34727,23 @@
         <v>0</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F10" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G10" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G10" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H10" s="77">
         <v>8000000</v>
       </c>
       <c r="I10" s="77"/>
       <c r="J10" s="79" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -34764,28 +34756,28 @@
         <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G11" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H11" s="77">
         <v>22600000</v>
       </c>
       <c r="I11" s="77" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="J11" s="78" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -34798,28 +34790,28 @@
         <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="F12" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G12" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H12" s="77">
         <v>17600000</v>
       </c>
       <c r="I12" s="77" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="J12" s="78" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -34832,28 +34824,28 @@
         <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F13" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G13" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G13" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H13" s="77">
         <v>155000000</v>
       </c>
       <c r="I13" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J13" s="79" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -34866,28 +34858,28 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1011</v>
       </c>
       <c r="F14" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G14" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G14" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H14" s="77">
         <v>700000</v>
       </c>
       <c r="I14" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J14" s="78" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -34900,28 +34892,28 @@
         <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D15" s="37" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F15" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H15" s="80" t="s">
         <v>1935</v>
       </c>
-      <c r="E15" s="37" t="s">
-        <v>1965</v>
-      </c>
-      <c r="F15" s="74" t="s">
-        <v>1914</v>
-      </c>
-      <c r="G15" s="75" t="s">
-        <v>1915</v>
-      </c>
-      <c r="H15" s="80" t="s">
+      <c r="I15" s="80" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J15" s="78" t="s">
         <v>1936</v>
-      </c>
-      <c r="I15" s="80" t="s">
-        <v>1980</v>
-      </c>
-      <c r="J15" s="78" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -34934,28 +34926,28 @@
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F16" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G16" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G16" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H16" s="77">
         <v>276000000</v>
       </c>
       <c r="I16" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J16" s="78" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -34968,28 +34960,28 @@
         <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F17" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G17" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H17" s="77">
         <v>12000000</v>
       </c>
       <c r="I17" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J17" s="78" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -35002,28 +34994,28 @@
         <v>56</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F18" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G18" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G18" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H18" s="77">
         <v>35000000</v>
       </c>
       <c r="I18" s="77" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="J18" s="78" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -35036,23 +35028,23 @@
         <v>0</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F19" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G19" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G19" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H19" s="77">
         <v>32000000</v>
       </c>
       <c r="I19" s="77"/>
       <c r="J19" s="78" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -35065,28 +35057,28 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1011</v>
       </c>
       <c r="F20" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G20" s="75" t="s">
         <v>1914</v>
-      </c>
-      <c r="G20" s="75" t="s">
-        <v>1915</v>
       </c>
       <c r="H20" s="77">
         <v>212000000</v>
       </c>
       <c r="I20" s="77" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J20" s="78" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -35099,28 +35091,28 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="D21" s="37" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F21" s="74" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G21" s="75" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H21" s="80" t="s">
         <v>1948</v>
       </c>
-      <c r="E21" s="37" t="s">
-        <v>1962</v>
-      </c>
-      <c r="F21" s="74" t="s">
-        <v>1914</v>
-      </c>
-      <c r="G21" s="75" t="s">
-        <v>1915</v>
-      </c>
-      <c r="H21" s="80" t="s">
+      <c r="I21" s="80" t="s">
+        <v>1978</v>
+      </c>
+      <c r="J21" s="78" t="s">
         <v>1949</v>
-      </c>
-      <c r="I21" s="80" t="s">
-        <v>1979</v>
-      </c>
-      <c r="J21" s="78" t="s">
-        <v>1950</v>
       </c>
     </row>
   </sheetData>
